--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -586,11 +586,10 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>この科目では、調査を作り、回答を数え、その数字から企画を決めて、SNSの投稿を作る仕事を学びます。
-好きに作るのではなく、数字にもとづいて「誰に・何を・いつ・どこで」を決めます。
-学校の方針として、日本語で調べる・数える・書く仕事を通して、日本語を使う力を高めます。
-進め方として、日本語がわからない時も、AIを使って自分で解決します。
-この科目で作る企画は、AI演習（実践）とビジネス情報リテラシーにつながります。前の科目の内容が、後の科目の採点項目になります。</t>
+          <t>調査を作り、回答を数え、その数字から企画を決めて、SNSの投稿を作る。
+「誰に・何を・いつ・どこで」は、数字にもとづいて決める。
+日本語で調べ・数え・書くことで、日本語を使う力を高める。わからない時はAIで自分で解決する。
+AI演習（実践）・ビジネス情報リテラシーにつながる。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -598,11 +597,10 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>教科書：『図解でわかる マーケティングの基本としくみ＜改訂2版＞』（学校指定。各回に対応するページを使う）
-基本教材：Geminiビジネス活用ガイド（目次に沿って、いまの最新の機能で扱う）
-必要な環境：スマホ（毎回使う）、個人の Google アカウント（無料）
-使うツール：Gemini アプリ、Google フォーム、スプレッドシート、スライド、ドライブ、カレンダー、Keep、Googleマップ、Googleトレンド、Google クラスルーム、Canva（無料版）
-成果物では、学生ごとに番号の違う回答データを配ります。</t>
+          <t>教科書：『図解でわかる マーケティングの基本としくみ＜改訂2版＞』
+基本教材：Geminiビジネス活用ガイド（最新の機能で扱う）
+環境：スマホ、個人の Google アカウント（無料）
+ツール：Gemini、フォーム、スプレッドシート、スライド、Googleマップ、Googleトレンド、Canva（無料版）</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -670,11 +668,10 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. 調べたいことに合う形式を選んで、Google フォームで調査票を作ることができる。
-2. 回答データからテスト送信や重複などの行を除き、スプレッドシートの関数で正しく数えることができる。
-3. 数えた数字と外のデータ（地図・検索の動き・アクセス解析）から、「誰に・何を・いつ・どこで」を決めることができる。
-4. Gemini と Canva を使って、数字と一致するSNSの投稿（複数ページの動画）と投稿文を作ることができる。
-5. 同じ指示文で画像を3回作り、3回とも条件どおりかを確かめることができる。</t>
+          <t>1. 目的に合う形式で調査フォームを作れる。
+2. 回答データを関数で正しく数えられる。
+3. 数字から「誰に・何を・いつ・どこで」を決められる。
+4. 数字と一致するSNS投稿と投稿文を作れる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -682,11 +679,9 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>合計100点で評価し、60点以上で単位を認めます。
-評定：A 90点以上、B 80点以上、C 70点以上、D 60点以上、E 59点以下。
-成果物は、課題ごとに決めた条件を満たしているかで採点します。
-数字は学生ごとに違うので、他の人の作品を写しても点になりません。
-学校の規程で、出席率が70%未満の場合は卒業できません。</t>
+          <t>100点満点で評価し、60点以上で単位を認める。
+評定：A 90〜、B 80〜、C 70〜、D 60〜、E 59以下。
+出席率70%未満は卒業できない（学校規程）。</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -754,10 +749,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>成果物（学習成果）80点：成果物1 8点、成果物2 12点、成果物3 15点、成果物4 20点、成果物5 25点。
-小テスト（学習姿勢）20点：成果物の本番の回を除く毎回（11回）行います。
-小テストは授業中だけ受け付け、満点になるまで再提出できます。満点になった回の数で点を計算します。
-欠席した回の小テストは点になりません。</t>
+          <t>成果物 80点（8・12・15・20・25点）
+小テスト 20点（成果物の回を除く11回。満点まで再提出可）</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -765,10 +758,8 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>小テストは、その場で結果がわかり、満点になるまで直して再提出できます。
-成果物の前の回に通し練習をし、採点の表で自己採点します。
-成果物の本番のあと、正解の見方を確かめて振り返ります。
-成果物の採点結果は、できた条件とできなかった条件がわかる形で返します。</t>
+          <t>小テスト：その場で結果を返し、満点まで再提出できる。
+成果物：前の回に通し練習と自己採点。本番の後に振り返る。</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -879,31 +870,30 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>マーケティングとは何か：売ることとの違い
+          <t>マーケティングとは何か
 教科書 p.12〜15</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>売ることとマーケティングの違いを、自分の言葉で説明できる。
-フォームで3つの形式の質問を作ることができる。</t>
+          <t>売ることとマーケティングの違いを説明できる。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>教科書でニーズに応える考え方を学ぶ。
-Gemini アプリの基本操作と、速いモデル・深いモデルの選び方を知る。
-投稿の骨子（主張→理由→具体例→CTA）を作り、フォームで3問を作る。</t>
+          <t>Gemini の基本操作。
+投稿の骨子（主張→理由→具体例→CTA）。
+フォームで3問を作る。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>フォーム（3問）を作り、教員を編集者に追加する</t>
+          <t>フォーム（3問）</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -921,30 +911,29 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>ニーズとベネフィット：調査から投稿までの練習
+          <t>ニーズとベネフィット
 教科書 p.56〜59</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>回答データを関数で数え、2枚の投稿にまとめることができる。</t>
+          <t>回答を関数で数え、2枚の投稿にまとめられる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>教科書でニーズ・ウォンツとベネフィットを学ぶ。
-Gemini の答えの根拠を確かめる。
-成果物1の通し練習：回答データのコピー、テスト送信に印、COUNTIF で数える、スライド2枚、画面録画、共有。</t>
+          <t>AIの答えの根拠を確かめる。
+成果物1の通し練習。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>成果物1の通し練習</t>
+          <t>成果物1の練習</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -962,28 +951,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>成果物1　調査から投稿までを一人で通す（実技）</t>
+          <t>成果物1　調査から投稿まで（実技）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>3問の調査フォームを作り、回答を数えた結果から2枚の投稿を時間内に作って提出できる。</t>
+          <t>調査から2枚の投稿を作って提出できる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業40分。スマホとAIを使ってよい。作業中は画面を録画する。
-終わったあと、正解の見方を確かめて振り返る。</t>
+          <t>説明10分、個人作業40分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>成果物1（フォーム・シート・スライド・画面録画）をクラスルームで提出</t>
+          <t>成果物1（クラスルーム）</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -993,8 +981,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定する。
-本人の証拠として録画を使う。</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -1006,20 +993,19 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>調査の方法と4P：質問の形式と割合の計算
+          <t>調査の方法と4P
 教科書 p.18〜19・48〜53・100〜101・112〜113・154</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>6つの形式で質問を作り、重複した回答を見分けて割合を計算できる。</t>
+          <t>6形式で質問を作り、重複を除いて割合を出せる。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>教科書でリサーチの方法、4P、製品と価格、AIDMA・AISAS を学ぶ。
-Gemini アプリに式を作らせ、スプレッドシートに貼る。
-フォームの6形式、重複の見分け方、ROUND で割合を出す。</t>
+          <t>Gemini に式を作らせて貼る。
+重複の見分け、ROUND で割合。</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1029,7 +1015,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1047,30 +1033,30 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>SNSマーケティング：画像生成と Canva
+          <t>SNSマーケティング
 教科書 p.166〜167</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Gemini で表紙の画像を作り、Canva で複数ページの投稿を動画にできる。</t>
+          <t>表紙の画像を作り、Canva で投稿動画にできる。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>教科書でSNSマーケティングを学ぶ。
-Gemini の画像生成で表紙を作る。Canva の使い方（サイズ、有料素材の見分け方、見本文字、MP4 で保存）。
-締切の日付を数え、成果物2の通し練習をする。</t>
+          <t>画像生成で表紙。
+Canva（サイズ・有料素材・MP4）。
+成果物2の通し練習。</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>成果物2の通し練習</t>
+          <t>成果物2の練習</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1088,27 +1074,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>成果物2　表紙と3ページの投稿を作る（実技）</t>
+          <t>成果物2　表紙と3ページの投稿（実技）</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>6問の調査フォームを作り、テスト送信と重複を除いて数えた結果から、表紙と3ページの投稿動画を時間内に作って提出できる。</t>
+          <t>表紙と3ページの投稿動画を作って提出できる。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業50分。スマホとAIを使ってよい。</t>
+          <t>説明10分、個人作業50分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>成果物2（フォーム・シート・Canva の MP4）をクラスルームで提出</t>
+          <t>成果物2（クラスルーム）</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -1118,7 +1104,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定する。</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -1130,20 +1116,19 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>STP：ターゲットを決めて数える
+          <t>STP・ターゲット
 教科書 p.20〜21・66〜67・74〜81</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>条件でターゲットを絞り、その人たちだけの人数と平均を出すことができる。</t>
+          <t>ターゲットを絞って人数と平均を出せる。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>教科書でSTP、ペルソナ、セグメンテーションを学ぶ。
-Gemini のガイド付き学習で、STP を対話で深く考える。
-COUNTIFS・AVERAGEIFS、表の形式の質問と星、除外する行に印をつける。作業録画と合言葉の練習。</t>
+          <t>ガイド付き学習でSTPを深める。
+COUNTIFS・AVERAGEIFS。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1153,7 +1138,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -1171,20 +1156,19 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ポジショニングと競合：地図で競合を調べる
+          <t>ポジショニングと競合
 教科書 p.90〜91・94〜95</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Googleマップで競合の評価と口コミの件数を比べ、競合を避ける時間を決めることができる。</t>
+          <t>地図で競合を比べ、避ける時間を決められる。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>教科書でポジショニングと5つの脅威を学ぶ。
-Gemini のディープリサーチで競合を下調べする。
-5ページの型を知り、表紙を3回作って3枚とも確かめる練習をする。</t>
+          <t>ディープリサーチで下調べ。
+表紙を3回作ってそろえる。</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1194,7 +1178,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -1212,27 +1196,27 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>成果物3　ターゲットと競合から5ページの投稿を作る（実技）</t>
+          <t>成果物3　ターゲットと競合から投稿（実技）</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ターゲットを絞って数え、競合を避けた時間を決めて、5ページの投稿動画と3回作った表紙を時間内に提出できる。</t>
+          <t>5ページの投稿動画と表紙3枚を提出できる。</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業60分。スマホとAIを使ってよい。作業中は画面を録画する。</t>
+          <t>説明10分、個人作業60分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>成果物3（フォーム・シート・Canva の MP4・表紙3枚・作業録画）をクラスルームで提出</t>
+          <t>成果物3（クラスルーム）</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -1242,8 +1226,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定する。
-本人の証拠として合言葉と録画を使う。</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -1255,20 +1238,19 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>検索とチャネル：Googleトレンドで言葉を選ぶ
+          <t>検索とチャネル
 教科書 p.124〜127・160〜161・168〜169</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Googleトレンドで言葉を比べ、日付と時刻の回答を時間帯ごとに数えることができる。</t>
+          <t>トレンドで言葉を比べ、時間帯ごとに数えられる。</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>教科書でSEO、AIマーケティング、流通チャネル、プッシュ・プル戦略を学ぶ。
-Gemini で条件と出力の形を指定して文章を作る。
-Googleトレンド（相対値、期間と地域）。日付・時刻の質問を作り、「時台」で数える。</t>
+          <t>Googleトレンド（期間・地域）。
+時刻の回答を「時台」で数える。</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1278,7 +1260,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -1296,20 +1278,19 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>アクセス解析とKPI：投稿先と日付を決める
+          <t>アクセス解析とKPI
 教科書 p.162〜163・174</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>アクセス解析の数字から投稿先を選び、そのサイズで棒グラフ入りのページと100字の投稿文を作ることができる。</t>
+          <t>投稿先を選び、グラフ入りのページと投稿文を作れる。</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>教科書でアクセス解析、KGI・KPI を学ぶ。
-Google アナリティクスの公式デモを教員の画面で見る。
-投稿先とサイズ、会場の予定から日付を選ぶ。Canva の棒グラフ。Gemini の Canvas で投稿文を直す。</t>
+          <t>アナリティクスのデモ（教員の画面）。
+Canva の棒グラフ、Canvas で投稿文。</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1319,7 +1300,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -1329,7 +1310,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>アナリティクスのデモは教員の画面で見る。</t>
+          <t>アナリティクスは教員の画面</t>
         </is>
       </c>
     </row>
@@ -1341,30 +1322,28 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>コミュニケーション・ミックス：通し練習と自己採点
+          <t>コミュニケーション・ミックス
 教科書 p.136〜139</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>成果物4を時間内に通して作り、採点の表で自分の作品を確かめることができる。</t>
+          <t>成果物4を通して作り、自己採点できる。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>教科書でコミュニケーション・ミックスを学ぶ。
-成果物4の通し練習（70分）。
-採点の表を Gemini に貼り、自分の作品を自己採点する。</t>
+          <t>成果物4の通し練習（70分）と自己採点。</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>成果物4の通し練習</t>
+          <t>成果物4の練習</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -1382,27 +1361,27 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>成果物4　3つのデータから投稿と投稿文を作る（実技）</t>
+          <t>成果物4　3つのデータから投稿（実技）</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>アンケート・トレンド・アクセス解析のデータから投稿先と日付を決め、5ページの投稿動画と100字の投稿文を時間内に提出できる。</t>
+          <t>投稿動画と投稿文を作って提出できる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業70分。スマホとAIを使ってよい。作業中は画面を録画する。</t>
+          <t>説明10分、個人作業70分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>成果物4（フォーム・シート・Canva の MP4・表紙3枚・投稿文・作業録画）をクラスルームで提出</t>
+          <t>成果物4（クラスルーム）</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -1412,8 +1391,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定する。
-本人の証拠として合言葉と録画を使う。</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -1425,20 +1403,19 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>マーケティング・オートメーション：例外の条件をあつかう
+          <t>マーケティング・オートメーション
 教科書 p.172〜173</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>祝日や投稿先の枚数の上限を考えて日付と投稿先を決め、150字の投稿文を作ることができる。</t>
+          <t>例外の条件を考えて日付と投稿先を決められる。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>教科書でマーケティング・オートメーションを学ぶ。
-Gemini アプリの連携アプリで、カレンダー・Keep に予定を入れる。
-祝日、X は4枚まで、ファイルのアップロードの質問。表紙の配色とレイアウトを3回そろえる。</t>
+          <t>連携アプリでカレンダーに予定を入れる。
+祝日・投稿の枚数上限・投稿文150字。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -1448,7 +1425,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -1466,30 +1443,28 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>マーケティングの5段階：全体の振り返りと予行
+          <t>全体の振り返り
 教科書 p.22〜25</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>最終課題と同じ形の課題を時間内に作り、できなかった点をやり直すことができる。</t>
+          <t>最終課題の形を通して作れる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>教科書でマーケティングの5段階を学び、全体を振り返る。
-最終課題の予行（別の番号のデータで70分）。
-自己採点して、できなかった点をやり直す。</t>
+          <t>最終課題の予行（70分）と自己採点。</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>最終課題の予行</t>
+          <t>最終課題の練習</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -1507,27 +1482,27 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>成果物5（最終課題）　調査から投稿までを誤りなく通す（実技）</t>
+          <t>成果物5（最終課題）（実技）</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>12問の調査から数えた数字だけで「誰に・何を・いつ・どこで」を決め、5ページの投稿動画と150字の投稿文を時間内に提出できる。</t>
+          <t>数字だけで企画を決め、投稿動画と投稿文を提出できる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業70分。スマホとAIを使ってよい。作業中は画面を録画する。</t>
+          <t>説明10分、個人作業70分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>成果物5（フォーム・シート・Canva の MP4・表紙3枚・作業録画）をクラスルームで提出</t>
+          <t>成果物5（クラスルーム）</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -1537,8 +1512,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定する。
-本人の証拠として合言葉と録画を使う。</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>

--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -669,7 +669,7 @@
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>1. 目的に合う形式で調査フォームを作れる。
-2. 回答データを関数で正しく数えられる。
+2. AIに作らせた式の結果を確かめ、回答を正しく数えられる。
 3. 数字から「誰に・何を・いつ・どこで」を決められる。
 4. 数字と一致するSNS投稿と投稿文を作れる。</t>
         </is>
@@ -679,9 +679,14 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>100点満点で評価し、60点以上で単位を認める。
-評定：A 90〜、B 80〜、C 70〜、D 60〜、E 59以下。
-出席率70%未満は卒業できない（学校規程）。</t>
+          <t>採点基準は学校規定に準ずる。
+【独自の基準】
+・成果物は、課題ごとに示した条件を1つずつ○✖で見て、○の分だけ点を足す。1か所まちがえても、ほかの点は失わない。
+・本人が作った証拠（合言葉・画面録画・版の履歴など）が無い提出は0点。
+・材料の数字は学生ごとに違う。他人の答えを写しても点にならない。
+・作業時間は目安で、採点しない。受付時間はクラスルームで課題ごとに設定する。
+・小テストは満点で○。点＝20×○の数÷11（成果物の回は行わない）。欠席は✖。
+・出席率70%の学生でも、成果物で48点取ればD（60点）に届く設計にしている。</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -917,7 +922,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>回答を関数で数え、2枚の投稿にまとめられる。</t>
+          <t>回答を正しく数え、2枚の投稿にまとめられる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1004,8 +1009,8 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Gemini に式を作らせて貼る。
-重複の見分け、ROUND で割合。</t>
+          <t>AIに式を作らせ、結果が正しいか確かめる。
+重複やテスト送信を見分ける。</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1128,7 +1133,7 @@
       <c r="D31" s="5" t="inlineStr">
         <is>
           <t>ガイド付き学習でSTPを深める。
-COUNTIFS・AVERAGEIFS。</t>
+AIに絞り込みの式を作らせ、数を確かめる。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1250,7 +1255,7 @@
       <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Googleトレンド（期間・地域）。
-時刻の回答を「時台」で数える。</t>
+時刻の回答を時間帯ごとに数える（式はAIに作らせる）。</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1771,10 +1776,14 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>合計60点以上で単位を認めます。
-成果物は、課題ごとに決めた条件を満たしているかで採点します。条件は、成果物ごとに前もって示します。
-出席率が70%未満の学生は、卒業できません（学校の規程）。
-評定: A 90点以上、B 80点以上、C 70点以上、D 60点以上、E 59点以下。</t>
+          <t>採点基準は学校規定に準ずる。
+【独自の基準】
+・成果物は、課題ごとに示した条件を1つずつ○✖で見て、○の分だけ点を足す。1か所まちがえても、ほかの点は失わない。
+・本人が作った証拠（合言葉・画面録画・版の履歴など）が無い提出は0点。
+・材料の数字は学生ごとに違う。他人の答えを写しても点にならない。
+・作業時間は目安で、採点しない。受付時間はクラスルームで課題ごとに設定する。
+・小テストは満点で○。点＝20×○の数÷13（成果物の回は行わない）。欠席は✖。
+・出席率70%の学生でも、成果物で48点取ればD（60点）に届く設計にしている。</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -2967,10 +2976,14 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>合計60点以上で単位を認めます。
-成果物は、課題ごとに決めた条件を満たしているかで採点します。条件は、成果物ごとに前もって示します。
-出席率が70%未満の学生は、卒業できません（学校の規程）。
-評定: A 90点以上、B 80点以上、C 70点以上、D 60点以上、E 59点以下。</t>
+          <t>採点基準は学校規定に準ずる。
+【独自の基準】
+・成果物は、課題ごとに示した条件を1つずつ○✖で見て、○の分だけ点を足す。1か所まちがえても、ほかの点は失わない。
+・本人が作った証拠（合言葉・画面録画・版の履歴など）が無い提出は0点。
+・材料の数字は学生ごとに違う。他人の答えを写しても点にならない。
+・作業時間は目安で、採点しない。受付時間はクラスルームで課題ごとに設定する。
+・小テストは満点で○。点＝20×○の数÷14（成果物の回は行わない）。欠席は✖。
+・出席率70%の学生でも、成果物で48点取ればD（60点）に届く設計にしている。</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>

--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -1004,12 +1004,13 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>6形式で質問を作り、重複を除いて割合を出せる。</t>
+          <t>6形式で質問を作り、AIの式の結果を2つ以上の方法で検算できる。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AIに式を作らせ、結果が正しいか確かめる。
+          <t>AIに式を作らせて貼る。
+検算：①答えのわかる小さな表で試す ②範囲をなぞり画面下の合計・個数と比べる ③見当と比べる。
 重複やテスト送信を見分ける。</t>
         </is>
       </c>
@@ -3568,7 +3569,8 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Gemini アプリに式を作らせ、スプレッドシートに貼って確かめる。
+          <t>Gemini アプリに式を作らせ、スプレッドシートに貼る。
+検算：①答えのわかる小さな表で試す ②範囲をなぞり画面下の合計・個数と比べる ③見当と比べる。
 画面録画をして、成果物3の通し練習をする。
 対応ページ（参考）: 単元5〜6 データベース p.28〜35</t>
         </is>

--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -1681,11 +1681,10 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>学校の方針は、日本語を使う力を伸ばすことです。この科目では、日本語で書かれたルールを読み、張り紙・スライド・表・画像を作ります。
-進め方: 日本語がわからない時も、AIを使って自分で解決します。
-AIの答えをそのまま使いません。原文と比べて、誤りを自分で直します。
-毎回、依頼を受けてから教員に届けるまでの仕事を、最初から最後まで一人で行います。回が進むと、材料と条件が増えます。
-3科目はつながっています。前の科目の内容が、後の科目の採点の項目になります。この科目は「形にする力」を担当します。</t>
+          <t>日本語で書かれたルールを読み、張り紙・スライド・表・画像を作る。
+AIの答えはそのまま使わず、原文と比べて誤りを自分で直す。
+依頼を受けてから届けるまでを一人で行う。回が進むと材料と条件が増える。
+わからない時はAIで自分で解決する。マーケティング・ビジネス情報リテラシーにつながる。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -1693,11 +1692,10 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>学校指定の教科書: ありません。
-基本教材: 『Geminiビジネス活用ガイド』の目次に沿って、いまの最新の機能で学びます。
-教員が作った材料（ルールの原文、AIが作った下書き、利用記録）を毎回配ります。
-必要なもの: スマホ（充電して持ってくる）、個人の Google アカウント（無料）。
-使うツール: Gemini アプリ、Gemini Notebook、画像生成、スプレッドシート、スライド、ドキュメント、ドライブ、Gmail、カレンダー、Meet、Google Classroom。</t>
+          <t>基本教材：Geminiビジネス活用ガイド（最新の機能で扱う）
+教員が作った材料（ルールの原文・AIの下書き・利用記録）を毎回配る
+環境：スマホ、個人の Google アカウント（無料）
+ツール：Gemini、Gemini Notebook、画像生成、スプレッドシート、スライド、ドキュメント、ドライブ、Gmail、カレンダー、Meet、クラスルーム</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -1765,11 +1763,10 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. ルールの原文だけを正として、AIが作った下書きの誤りを見つけて直すことができる。
-2. 数字を手で打たず、スプレッドシートの式で集計表を作ることができる。
-3. 決めた条件を守った画像を、同じ指示で3枚そろえて作ることができる。
-4. 決められた形の約束どおりに、説明のスライドを作ることができる。
-5. 作ったものを、メール・共有・予定の招待で依頼した人に届けることができる。</t>
+          <t>1. 原文だけを正として、AIの下書きの誤りを直せる。
+2. AIに作らせた式の結果を確かめ、集計表を作れる。
+3. 条件を守った画像を3枚そろえ、約束どおりのスライドを作れる。
+4. 作ったものをメール・共有・予定の招待で届けられる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1852,11 +1849,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>成果物 80点: 成果物1（8点）、成果物2（12点）、成果物3（15点）、成果物4（20点）、成果物5（25点）。
-小テスト 20点: 成果物の本番の回（5回）を除く13回で行います。満点まで何回でも出し直せます。
-小テストの点 ＝ 20 × 満点になった回数 ÷ 13。
-小テストは授業中だけ受け付けます。欠席した回は0になります。
-期末試験はありません。合計100点。</t>
+          <t>成果物 80点（8・12・15・20・25点）
+小テスト 20点（成果物の回を除く13回。満点まで再提出可）</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1864,10 +1858,8 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>小テスト: その場で結果が出ます。満点になるまで出し直せます。
-成果物: 本番の次の回に答え合わせをします（5・9・13・16回）。
-どこでまちがえやすいか、次に何をすればよいかを説明します。
-次の成果物では、同じ仕事に新しい条件を足して練習します。</t>
+          <t>小テスト：その場で結果を返し、満点まで再提出できる。
+成果物：本番の次の回に答え合わせをする（5・9・13・16回）。</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -1978,30 +1970,30 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ガイダンス　ファイルを教員に届ける
-（基本教材 第2章1 基本操作）</t>
+          <t>ガイダンス・ファイルの提出
+基本教材 2章1</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>自分のアカウントで作ったファイルを、教員に届く形で提出できる</t>
+          <t>作ったファイルを教員に届く形で提出できる。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>科目の進め方と評価を説明する。
-ファイルのコピー、ファイル名と合言葉、教員への共有を練習する。
-Gemini Notebook に文章を貼る</t>
+          <t>科目の進め方と評価。
+ファイル名と合言葉、教員への共有。
+Gemini Notebook に文章を貼る。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>練習の提出（クラスルーム）</t>
+          <t>練習の提出</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2009,11 +2001,7 @@
           <t>小テスト</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>個人の Google アカウントとスマホを使う</t>
-        </is>
-      </c>
+      <c r="H25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -2024,28 +2012,28 @@
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>原文を正として張り紙を直す
-（基本教材 第5章1 Gemini Notebook）</t>
+基本教材 5章1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>原文だけを正として、下書きの数字・条件・誤字を直せる</t>
+          <t>原文だけを正として下書きを直せる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Gemini Notebook に原文を入れ、原文だけを根拠に答えさせる。
-照合表を作り、張り紙の下書きを直す（練習版）</t>
+          <t>Gemini Notebook で原文だけを根拠に答えさせる。
+照合表を作り、張り紙を直す。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>練習版の張り紙</t>
+          <t>張り紙の練習</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2063,30 +2051,30 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>式で数える・画像の画風を変える
-（基本教材 第3章5 ITツール活用、第2章6 画像生成）</t>
+          <t>式で数える・画像の画風
+基本教材 3章5・2章6</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>数字を手で打たずに式で数え、保つ点を指示して画像を作れる</t>
+          <t>AIの式で数え、保つ点を守って画像を作れる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Gemini アプリに式を作らせ、スプレッドシートで数える。
-画像生成で画風を変え、保つ点を守る。
-スライド1枚を作る。30分の通し練習</t>
+          <t>AIに式を作らせ、結果を確かめる。
+画像生成で画風を変える。スライド1枚。
+成果物1の通し練習（30分）。</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>練習版の一式（張り紙・スライド・集計・画像）</t>
+          <t>成果物1の練習</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2104,28 +2092,27 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>成果物1　小さな一連の仕事を一人で通す（実技）</t>
+          <t>成果物1　4つを一人で通す（実技）</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>原文を正として、張り紙・スライド1枚・式で数える集計表・画像の4つを作り、時間内に提出できる</t>
+          <t>張り紙・スライド・集計表・画像を作って提出できる。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業30分。
-スマホとAIを使ってよい。</t>
+          <t>説明10分、個人作業30分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>成果物1（張り紙・スライド・集計表・画像）をクラスルームで提出</t>
+          <t>成果物1（クラスルーム）</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2135,7 +2122,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠としてファイル名の合言葉と作成時刻を使う</t>
+          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
         </is>
       </c>
     </row>
@@ -2147,29 +2134,29 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>成果物1の答え合わせ　誤りを探し切る
-（基本教材 第1章6 Gemini Notebook、第3章2 情報収集）</t>
+          <t>誤りを探し切る
+基本教材 1章6・3章2</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>下書きの誤りを、数を知らされずに探し切れる</t>
+          <t>下書きの誤りを数を知らされずに探し切れる。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>成果物1の答え合わせをする。
-6件の照合と、読めるのに意味が違う誤字を練習する</t>
+          <t>成果物1の答え合わせ。
+6件の照合、意味が違う誤字の練習。</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>なし（小テストのみ）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2187,30 +2174,29 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>スライドの形の約束・上限ちょうどの数え方
-（基本教材 第3章3 文章作成、第3章5 ITツール活用）</t>
+          <t>スライドの形・上限ちょうど
+基本教材 3章3・3章5</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>AIの出力を約束どおりの形に直せる。上限ちょうどの行を正しく数えられる</t>
+          <t>出力を約束どおりの形に直し、上限ちょうどを正しく数えられる。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
           <t>出力の形を指示して文章を作る。
-スライドを形の約束に合わせて直す。
-「上限ちょうどは違反でない」式を作る</t>
+「上限ちょうどは違反でない」式をAIに作らせ、確かめる。</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>練習版のスライドと集計表</t>
+          <t>スライドと集計表の練習</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2228,29 +2214,29 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>同じ指示で画像を3枚そろえる
-（基本教材 第2章6 画像生成）</t>
+          <t>画像を3枚そろえる
+基本教材 2章6</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>同じ条件の画像を3枚そろえ、1枚ずつ○✖で確かめられる</t>
+          <t>同じ条件の画像を3枚そろえ、1枚ずつ確かめられる。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>同じ指示で画像を3枚作り、保つ点を1枚ずつ確かめる。
-40分の通し練習</t>
+          <t>同じ指示で3枚作り、保つ点を確かめる。
+成果物2の通し練習（40分）。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>練習版の一式</t>
+          <t>成果物2の練習</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2268,28 +2254,27 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>成果物2　条件の増えた一連の仕事を通す（実技）</t>
+          <t>成果物2　条件の増えた一連の仕事（実技）</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>下書きの誤りを直し、形の約束を守ったスライド・上限ちょうどを正しく数える集計表・画像3枚を作って提出できる</t>
+          <t>誤りを直し、スライド・集計表・画像3枚を提出できる。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業40分。
-スマホとAIを使ってよい。</t>
+          <t>説明10分、個人作業40分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>成果物2（張り紙・スライド・集計表・画像3枚）をクラスルームで提出</t>
+          <t>成果物2（クラスルーム）</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2299,7 +2284,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠としてファイル名の合言葉と作成時刻を使う</t>
+          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
         </is>
       </c>
     </row>
@@ -2311,30 +2296,29 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>成果物2の答え合わせ　古い値と逆の文を見抜く
-（基本教材 第3章3 文章作成）</t>
+          <t>古い値と逆の文を見抜く
+基本教材 3章3</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>旧版の値と、原文と逆の文を見抜き、誤りの一覧を作れる</t>
+          <t>旧版の値と原文と逆の文を見抜き、誤り一覧を作れる。</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>成果物2の答え合わせをする。
-改定の記録を読み、原文と逆の文を探す。
-条件・例・出力の形を指示して誤り一覧を作る</t>
+          <t>成果物2の答え合わせ。
+改定の記録を読み、誤り一覧を作る。</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>練習版の誤り一覧</t>
+          <t>誤り一覧の練習</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2352,29 +2336,29 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>行を足しても正しく変わる表
-（基本教材 第3章5 ITツール活用）</t>
+          <t>行を足しても正しい表
+基本教材 3章5</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>延長と停止の開始日を式で出し、自分で行を足して確かめられる</t>
+          <t>延長と停止の開始日を出し、行を足して確かめられる。</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>延長・停止の開始日を式で出す。
-自分で行を足して、結果が正しく変わるか確かめる</t>
+          <t>開始日の式をAIに作らせる。
+行を足して結果が正しく変わるか確かめる。</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>練習版の集計表</t>
+          <t>集計表の練習</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2393,29 +2377,29 @@
       <c r="B35" s="5" t="inlineStr">
         <is>
           <t>メールで納品する
-（基本教材 第3章3 文章作成）</t>
+基本教材 3章3</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>集計の結果を報告メールに正しく書き、Gmail で納品できる</t>
+          <t>集計の結果をメールに正しく書き、納品できる。</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>スライド3枚を作り、画像から物を消す。
-Gemini アプリで納品メールの下書きを作り、Gmail で送る。
-50分の通し練習</t>
+          <t>スライド3枚、画像から物を消す。
+Gemini で下書きし、Gmail で送る。
+成果物3の通し練習（50分）。</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>練習版の納品メール</t>
+          <t>成果物3の練習</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2433,28 +2417,27 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>成果物3　罠の増えた一連の仕事をメールで納品する（実技）</t>
+          <t>成果物3　メールで納品する（実技）</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>旧版の値と逆の文を直し、延長と停止日を式で出し、誤り一覧と画像3枚をそろえてメールで納品できる</t>
+          <t>誤り一覧・集計表・画像3枚をそろえ、メールで納品できる。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業50分。
-スマホとAIを使ってよい。</t>
+          <t>説明10分、個人作業50分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>成果物3（張り紙・スライド・集計表・誤り一覧・画像3枚・納品メール）をクラスルームで提出</t>
+          <t>成果物3（クラスルーム）</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2464,7 +2447,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠としてファイル名の合言葉と作成時刻を使う</t>
+          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
         </is>
       </c>
     </row>
@@ -2476,30 +2459,29 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>成果物3の答え合わせ　スライドを作り直す
-（基本教材 第2章4 Canvas）</t>
+          <t>スライドを作り直す
+基本教材 2章4</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>書かれていないこと・重複・詰め込みを見つけ、スライドを作り直せる</t>
+          <t>書かれていないこと・重複・詰め込みを直せる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>成果物3の答え合わせをする。
-Canvas で、1枚に1つの話のスライドに作り直す。
-同じ頼み方で2枚を作り、そろうか確かめる</t>
+          <t>成果物3の答え合わせ。
+Canvas で1枚1つの話に作り直す。</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>練習版のスライド</t>
+          <t>スライドの練習</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2518,29 +2500,28 @@
       <c r="B38" s="5" t="inlineStr">
         <is>
           <t>集計・グラフ・予定をそろえる
-（基本教材 第2章9 連携アプリ）</t>
+基本教材 2章9</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>集計とグラフと報告の数字をそろえ、訂正後の時刻で説明会に招待できる</t>
+          <t>集計・グラフ・報告の数字をそろえ、説明会に招待できる。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>月で数え直す式と、部屋ごとの件数・グラフを作る。
-画像に文字を入れる。
-カレンダーに Meet つきの予定を作り、招待する</t>
+          <t>月で数え直す式とグラフをAIと作る。画像に文字を入れる。
+カレンダーに Meet つきの予定を作り招待する。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>練習版の集計表と予定</t>
+          <t>集計表と予定の練習</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2550,7 +2531,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>連携アプリは「アクティビティを保存」をオンにして使う</t>
+          <t>連携アプリは「アクティビティを保存」をオン</t>
         </is>
       </c>
     </row>
@@ -2562,28 +2543,27 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>成果物4　最終課題に近い一連の仕事を通す（実技）</t>
+          <t>成果物4　最終課題に近い一連の仕事（実技）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AIが作ったスライドを原文と集計どおりに作り直し、集計表・画像3枚・納品メール・説明会の招待までを提出できる</t>
+          <t>スライド・集計表・画像3枚・納品メール・招待を提出できる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業70分。
-スマホとAIを使ってよい。</t>
+          <t>説明10分、個人作業70分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>成果物4（スライド・集計表・画像3枚・納品メール・説明会の予定）をクラスルームで提出</t>
+          <t>成果物4（クラスルーム）</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -2593,7 +2573,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠としてファイル名の合言葉と作成時刻を使う</t>
+          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
         </is>
       </c>
     </row>
@@ -2605,30 +2585,29 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>成果物4の答え合わせ　期間で変わる条件
-（基本教材 第2章2 モデルの選び方、第5章3 Gemini Notebook の活用）</t>
+          <t>期間で変わる条件
+基本教材 2章2・5章3</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>日付の範囲で条件が変わる集計と、過不足のない誤り一覧を作れる</t>
+          <t>期間で条件が変わる集計と誤り一覧を作れる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>成果物4の答え合わせをする。
-Flash（速い）と Pro（深い）を比べて使い分ける。
-条番号つきの誤り一覧と、期間で上限が変わる式を練習する</t>
+          <t>成果物4の答え合わせ。
+Flash と Pro の使い分け。</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>なし（小テストのみ）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2647,28 +2626,28 @@
       <c r="B41" s="5" t="inlineStr">
         <is>
           <t>最終課題の通し練習
-（基本教材 第2章7 学習モード）</t>
+基本教材 2章7</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>4つを時間内に仕上げ、画面録画を途切れさせずに提出できる</t>
+          <t>4つを時間内に仕上げ、画面録画つきで提出できる。</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>ガイド付き学習で、自分の誤りを振り返る。
-最終課題の通し練習をする（60分で送信、画面録画も）</t>
+          <t>ガイド付き学習で自分の誤りを振り返る。
+最終課題の通し練習（60分、画面録画）。</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>練習の画面録画</t>
+          <t>最終課題の練習（画面録画）</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2686,29 +2665,27 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>成果物5　原文だけを正として4つを誤りゼロで仕上げる（実技）</t>
+          <t>成果物5　4つを誤りゼロで仕上げる（実技）</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>一人で、原文だけを正として張り紙・スライド・画像・数式で動く集計表の4つを誤りなく仕上げられる</t>
+          <t>原文だけを正として4つを誤りなく仕上げられる。</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業90分。
-スマホとAIを使ってよい。
-作業中は画面を録画する</t>
+          <t>説明10分、個人作業90分。スマホ・AI使用可。作業中は画面録画。</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>成果物5（張り紙・スライド・画像・集計表・画面録画）をクラスルームで提出</t>
+          <t>成果物5（クラスルーム）</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2718,7 +2695,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠として合言葉と録画を使う。録画のリンクは次の授業の開始までに出す</t>
+          <t>受付はクラスルームで設定。本人の証拠は合言葉と画面録画（リンクは次の授業の開始まで）</t>
         </is>
       </c>
     </row>
@@ -2881,11 +2858,10 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>学校の方針は、日本語を使う力を伸ばすことです。この科目では、日本語で書かれたルール・メール・申込データを読み、仕事の連絡と記録を正しく行います。
-進め方: 日本語がわからない時も、AIを使って自分で解決します。AIの答えは、ルールと照らして自分で確かめます。
-扱うのは、AI・ITのうち仕事で使う範囲です（メールの宛先、共有の設定、個人情報・著作権、データの数え方）。
-架空の学内講座の運営を、最初から最後まで一人（成果物2は2人1組）で行います。回が進むと、材料と条件が増えます。
-3科目はつながっています。前の科目の内容が、後の科目の採点の項目になります。この科目は「運用する力」を担当します。</t>
+          <t>仕事のルール・メール・申込データを日本語で読み、連絡と記録を正しく行う。
+架空の学内講座の運営を一人（成果物2は2人1組）で行い、回ごとに材料と条件が増える。
+扱うのはメールの宛先、共有の設定、個人情報・著作権、データの数え方。わからない時はAIで自分で解決し、ルールと照らして確かめる。
+マーケティング・AI演習（実践）につながり、この科目は「運用する力」を担う。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -2893,11 +2869,11 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>学校指定の教科書: 『留学生のためのITリテラシー』（参考として使います。対応ページを授業計画に書きます）。
-基本教材: 『Geminiビジネス活用ガイド』の目次に沿って、いまの最新の機能で学びます。
-教員が作った材料（運営のルール、メール、申込データ、前任者の下書き）を配ります。
-必要なもの: スマホ（充電して持ってくる）、個人の Google アカウント（無料）。
-使うツール: Gemini アプリ、Gemini Notebook、Gmail、カレンダー、Meet、Keep、ドキュメント、ドライブ、スプレッドシート、フォーム、フォト、YouTube、画面録画、Google Classroom。</t>
+          <t>教科書：『留学生のためのITリテラシー』（参考。対応ページを授業計画に示す）
+基本教材：Geminiビジネス活用ガイド（最新の機能で扱う）
+配布：運営のルール、メール、申込データ、前任者の下書き
+環境：スマホ、個人の Google アカウント（無料）
+ツール：Gemini、Gemini Notebook、Gmail、カレンダー、Meet、Keep、ドキュメント、ドライブ、スプレッドシート、フォーム、フォト、YouTube、画面録画、Classroom</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -2965,11 +2941,10 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. いくつかのメールから最新の決定を拾い、正しい宛先（BCC など）でメールを送ることができる。
-2. 会議を招待して開き、議事録と ToDo の期限をルールどおりに作ることができる。
-3. 共有フォルダを整理し、共有の設定を安全に直すことができる。
-4. スプレッドシートの式で申込を数え、先着順で確定と補欠を決めることができる。
-5. 前任者の下書きの誤りだけを、ルールと照らして直すことができる。</t>
+          <t>1. メールから最新の決定を拾い、下書きの誤りだけを直して、正しい宛先（BCC など）で送れる。
+2. 会議を開き、議事録と ToDo の期限をルールどおりに作れる。
+3. 共有フォルダを整理し、共有の設定を安全に直せる。
+4. AIに作らせた式の結果を確かめ、申込を数えて確定と補欠を決められる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -3052,11 +3027,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>成果物 80点: 成果物1（8点）、成果物2（12点）、成果物3（15点）、成果物4（20点）、成果物5（25点）。
-小テスト 20点: 成果物の本番の回（5回）を除く14回で行います。満点まで何回でも出し直せます。
-小テストの点 ＝ 20 × 満点になった回数 ÷ 14。
-小テストは授業中だけ受け付けます。欠席した回は0になります。
-期末試験はありません。合計100点。</t>
+          <t>成果物 80点（8・12・15・20・25点）
+小テスト 20点（成果物の回を除く14回。授業中のみ、満点まで再提出可）</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -3064,11 +3036,8 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>小テスト: その場で結果が出ます。満点になるまで出し直せます。
-成果物: 本番の前の回に、別の番号の材料で通し練習をします（2・6・10・14・18回）。14・18回は自己採点もします。
-成果物1は、本番の回の中で答え合わせをします。
-採点のあと、どこでまちがえやすいか、次に何をすればよいかを説明します。
-次の成果物では、同じ仕事に新しい条件を足して練習します。</t>
+          <t>小テスト：その場で結果を返し、満点まで再提出できる。
+成果物：前の回に別の番号の材料で通し練習（14・18回は自己採点も）。成果物1は本番の回で答え合わせ。採点の後に振り返る。</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -3179,30 +3148,30 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ガイダンス　メールの宛先と曜日を確かめる
-（基本教材 第2章1 基本操作）</t>
+          <t>ガイダンス・メールの宛先
+基本教材 第2章1／教科書 p.40〜43</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>To・CC・BCC を使い分けてメールを送り、カレンダーで曜日を確かめられる</t>
+          <t>To・CC・BCC を使い分けて送り、曜日を確かめられる。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>科目の進め方と評価を説明する。
-Gmail の To・CC・BCC、カレンダーでの曜日の確認、提出フォームを練習する。
-対応ページ（参考）: 単元8 インターネット技術 p.40〜43</t>
+          <t>科目の進め方と評価。
+Gmail の To・CC・BCC、カレンダーで曜日の確認。
+提出フォームの練習。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>練習の提出（提出フォーム）</t>
+          <t>練習の提出</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3210,11 +3179,7 @@
           <t>小テスト</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>個人の Google アカウントとスマホを使う</t>
-        </is>
-      </c>
+      <c r="H25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3224,30 +3189,29 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>日程変更の返信を通しで練習する
-（基本教材 第3章3 文章作成）</t>
+          <t>日程変更の返信
+基本教材 第3章3／教科書 p.44〜47</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>いちばん新しい合意を拾い、正しい宛先で日程確定のメールを送れる</t>
+          <t>最新の合意を拾い、正しい宛先で確定のメールを送れる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Gemini アプリに返信の下書きを作らせ、運営の決まりと照らして直す。
-成果物1の通し練習（別の番号の材料）。
-対応ページ（参考）: 単元9 情報セキュリティの概要 p.44〜47</t>
+          <t>AIに返信の下書きを作らせ、決まりと照らして直す。
+成果物1の通し練習（別の番号の材料）。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>練習のメール</t>
+          <t>成果物1の練習</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -3265,29 +3229,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>成果物1　日程変更の連絡に返信する（実技）</t>
+          <t>成果物1　日程変更への返信（実技）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>4通のメールから最新の日にち・曜日・時間・会場を拾い、BCC で日程確定のメールを1通送れる</t>
+          <t>最新の日時・会場を拾い、BCC で確定のメールを送れる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業20分。
-スマホとAIを使ってよい。
-作業のあと、答え合わせをする</t>
+          <t>説明10分、個人作業20分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>成果物1（日程確定のメール）を送り、提出フォームで提出</t>
+          <t>成果物1（提出フォーム）</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3297,7 +3259,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠として、メールの差出人と提出フォームのアドレスを照らす</t>
+          <t>受付はクラスルームで設定。証拠はメールの差出人と提出フォームのアドレスの照合</t>
         </is>
       </c>
     </row>
@@ -3309,20 +3271,19 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>会議を招待して開く
-（基本教材 第2章1 基本操作）</t>
+          <t>会議の招待
+基本教材 第2章1／教科書 p.36〜39</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>カレンダーから招待して Meet を開き、チャットで話し合える</t>
+          <t>カレンダーから招待して Meet を開き、チャットで話し合える。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>カレンダーから招待し、Meet を開いてチャットで話す。
-Keep のチェックリストで分担を書く。Gemini アプリの履歴と名前の変更。
-対応ページ（参考）: 単元7 ネットワークの基本構成 p.36〜39</t>
+          <t>カレンダーから招待し、Meet のチャットで話す。
+Keep のチェックリストで分担。Gemini の履歴と名前の変更。</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3332,7 +3293,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3350,20 +3311,19 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>議事録を取り、ToDo の期限を決める
-（基本教材 第3章3 文章作成）</t>
+          <t>議事録と ToDo の期限
+基本教材 第3章3／教科書 p.88〜91・104〜107</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>話し合いから議事録を作り、ToDo の期限を曜日と決まりどおりに計算できる</t>
+          <t>議事録を作り、ToDo の期限を決まりどおりに出せる。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Gemini アプリで議事録の型を作り、話していないことが足されていないか確かめる。
-ToDo の分担と、期限の計算（営業日・曜日）。
-対応ページ（参考）: 単元20 p.88〜91、単元24 p.104〜107</t>
+          <t>AIで議事録の型を作り、話していないことが足されていないか確かめる。
+期限の計算（営業日・曜日）。</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3373,7 +3333,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3391,30 +3351,29 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>運営会議を通しで練習する（2人1組）
-（基本教材 第5章1 Gemini Notebook）</t>
+          <t>運営会議の練習（2人1組）
+基本教材 第5章1／教科書 p.76〜79</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>議事録から要点を出させ、元の議事録と照らして確かめられる</t>
+          <t>議事録の要点を出させ、元と照らして確かめられる。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Gemini Notebook に議事録を入れ、要点を出させて元と照らす。
-成果物2の通し練習（2人1組、短い版）。
-対応ページ（参考）: 単元17 システム開発技術 p.76〜79</t>
+          <t>Gemini Notebook で議事録の要点を出させ、元と照らす。
+成果物2の通し練習（2人1組、短い版）。</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>練習の招待・議事録</t>
+          <t>成果物2の練習</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3432,29 +3391,28 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>成果物2　運営会議を開いて、決めたことを動かす（実技・2人1組）</t>
+          <t>成果物2　運営会議（実技・2人1組）</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>会議を招待して開き、議事録を正しい宛先で送り、ToDo を正しい期限でカレンダーに入れられる</t>
+          <t>会議を開き、議事録を正しい宛先で送り、ToDo を期限どおりに入れられる。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、2人1組で作業し、授業開始から85分を目安に提出する。
-会議は Meet のチャットで2回（各15分）。
-スマホとAIを使ってよい</t>
+          <t>説明10分、2人1組で作業し開始から85分を目安に提出。スマホ・AI使用可。
+会議は Meet のチャットで2回（各15分）。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>成果物2（会議の招待・議事録・送付のメール・Keep の分担・ToDo の予定）を提出フォームで提出</t>
+          <t>成果物2（提出フォーム）</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3464,7 +3422,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠として合言葉と版の履歴を使う。人数が奇数の時は1組だけ3人</t>
+          <t>受付はクラスルームで設定。証拠は合言葉と版の履歴。奇数の時は1組だけ3人</t>
         </is>
       </c>
     </row>
@@ -3476,20 +3434,19 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>共有フォルダを整理する
-（基本教材 第2章1 基本操作）</t>
+          <t>共有フォルダの整理
+基本教材 第2章1／教科書 p.24〜27・48〜51</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ファイル名ではなく中身の日付で最新版を見分け、決まりどおりに名前を変えて整理できる</t>
+          <t>中身の日付で最新版を見分け、決まりどおりに整理できる。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>ドライブで名前の変更・フォルダの作成・移動をする。
-中身の日付で最新版を見分ける。
-対応ページ（参考）: 単元4 p.24〜27、単元10 p.48〜51</t>
+          <t>ドライブで名前の変更・フォルダ作成・移動。
+中身の日付で最新版を見分ける。</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3499,7 +3456,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3517,20 +3474,20 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>安全な共有と写真の扱い
-（基本教材 第3章2 情報収集）</t>
+          <t>安全な共有と写真
+基本教材 第3章2／教科書 p.56〜59</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>リンク公開を止めて閲覧者・編集者を正しく設定し、写真を必要な人だけに共有できる</t>
+          <t>リンク公開を止め、閲覧者・編集者を正しく設定できる。</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Gemini アプリに、写真の写り込みと撮影場所の確かめ方を聞く。
-共有の設定（リンク公開を止める、閲覧者と編集者、学外への名簿）。フォトのアルバムと切り取り。
-対応ページ（参考）: 単元12 認証技術 p.56〜59</t>
+          <t>AIに写り込みと撮影場所の確かめ方を聞く。
+共有の設定（リンク公開、閲覧者・編集者、学外への名簿）。
+フォトのアルバムと切り取り。</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -3540,7 +3497,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3558,31 +3515,30 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>申込を式で数える
-（基本教材 第3章5 ITツール活用）</t>
+          <t>申込を数える
+基本教材 第3章5／教科書 p.28〜35</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>空白・取消・申し込み直し・締切後を正しく扱う式で、申込の人数を出せる</t>
+          <t>空白・取消・申し込み直し・締切後を正しく扱い、人数を出せる。</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Gemini アプリに式を作らせ、スプレッドシートに貼る。
+          <t>AIに式を作らせて貼る。
 検算：①答えのわかる小さな表で試す ②範囲をなぞり画面下の合計・個数と比べる ③見当と比べる。
-画面録画をして、成果物3の通し練習をする。
-対応ページ（参考）: 単元5〜6 データベース p.28〜35</t>
+画面録画をして成果物3の通し練習。</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>練習のシート・画面録画</t>
+          <t>成果物3の練習</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3600,29 +3556,27 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>成果物3　引き継いだ共有フォルダを整理して、人数を報告する（実技）</t>
+          <t>成果物3　共有フォルダの整理と人数の報告（実技）</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>フォルダを決まりどおりに整理して危ない共有を止め、式で出した人数をメールで報告できる</t>
+          <t>フォルダを整理して危ない共有を止め、人数をメールで報告できる。</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業45分。
-スマホとAIを使ってよい。
-作業中は画面を録画する</t>
+          <t>説明10分、個人作業45分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>成果物3（整理したフォルダ・集計のシート・アルバム・報告メール・画面録画）を提出フォームで提出</t>
+          <t>成果物3（提出フォーム）</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3632,7 +3586,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠として合言葉と録画を使う。録画が授業中に上がらない時は、次の授業の開始までに出す</t>
+          <t>受付はクラスルームで設定。証拠は合言葉と録画。録画は次の授業の開始まで可</t>
         </is>
       </c>
     </row>
@@ -3644,20 +3598,19 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>先着順で確定と補欠を決める
-（基本教材 第3章5 ITツール活用）</t>
+          <t>先着順で確定と補欠
+基本教材 第3章5／教科書 p.80〜83</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>最新の回答だけを残して時刻の順に並べ、定員で確定と補欠に分けられる</t>
+          <t>最新の回答だけを残し、定員で確定と補欠に分けられる。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>関数で最新の回答だけを残し、時刻の順に並べる。
-定員を超えた人を補欠にする。
-対応ページ（参考）: 単元18 データ構造とアルゴリズム p.80〜83</t>
+          <t>AIに式を作らせ、最新の回答だけを残して時刻順に並べる。
+定員を超えた人を補欠にする。</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -3667,7 +3620,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -3685,20 +3638,19 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>お知らせの誤りだけを直す
-（基本教材 第3章3 文章作成）</t>
+          <t>誤りだけを直す
+基本教材 第3章3／教科書 p.64〜67・92〜95</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>下書きの誤りだけを直し（直しすぎない）、データを変えても正しい式か確かめられる</t>
+          <t>下書きの誤りだけを直し、データを変えても式が正しいか確かめられる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Gemini アプリの直しを、決まりと照らして選ぶ。
-データを差し替えて、式の結果が正しく変わるか確かめる。
-対応ページ（参考）: 単元14 p.64〜67、単元21 p.92〜95</t>
+          <t>AIの直しを決まりと照らして選ぶ（直しすぎない）。
+データを差し替えて式の結果を確かめる。</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3708,7 +3660,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3726,30 +3678,29 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>補欠のお知らせを通しで練習する
-（基本教材 第2章7 学習モード）</t>
+          <t>補欠のお知らせの練習
+基本教材 第2章7／教科書 p.72〜75</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>40分の通し練習をして、自分の誤りを採点の表で見つけられる</t>
+          <t>通し練習をして、採点の表で自分の誤りを見つけられる。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
           <t>成果物4の通し練習（40分）と自己採点。
-ガイド付き学習で、自分の誤りを振り返る。
-対応ページ（参考）: 単元16 ヒューマンインタフェース技術 p.72〜75</t>
+ガイド付き学習で誤りを振り返る。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>練習のシート・自己採点</t>
+          <t>成果物4の練習</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -3767,29 +3718,27 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>成果物4　申込から補欠を決めて、補欠のお知らせを出す（実技）</t>
+          <t>成果物4　補欠の決定とお知らせ（実技）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>式で人数を出して先着順で補欠を決め、下書きの誤りだけを直して、補欠の方に BCC で予約送信できる</t>
+          <t>補欠を決め、下書きを直して補欠の方に BCC で予約送信できる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業40分。
-スマホとAIを使ってよい。
-作業中は画面を録画する</t>
+          <t>説明10分、個人作業40分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>成果物4（式のシート・返信記録のシート・お知らせのメール・画面録画〈YouTube 限定公開〉）を提出フォームで提出</t>
+          <t>成果物4（提出フォーム）</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -3799,7 +3748,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠として合言葉と録画を使う。録画が授業中に上がらない時は、次の授業の開始までに出す</t>
+          <t>受付はクラスルームで設定。証拠は合言葉と録画（YouTube 限定公開）。録画は次の授業の開始まで可</t>
         </is>
       </c>
     </row>
@@ -3811,20 +3760,19 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>改定のあるルールと表記ゆれ
-（基本教材 第5章1 Gemini Notebook）</t>
+          <t>改定ルールと表記ゆれ
+基本教材 第5章1／教科書 p.52〜55・96〜99</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>改定後のルールを使い、表記ゆれ（全角・古い選択肢）をそろえて数えられる</t>
+          <t>改定後のルールで、表記ゆれをそろえて数えられる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Gemini Notebook にルールを入れ、ルールを根拠に答えさせる。
-表記ゆれをそろえて数える。
-対応ページ（参考）: 単元11 p.52〜55、単元22 p.96〜99</t>
+          <t>Gemini Notebook にルールを入れ、根拠つきで答えさせる。
+表記ゆれ（全角・古い選択肢）をそろえて数える。</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3834,7 +3782,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -3852,20 +3800,19 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>録画・画像・名簿の扱いと費用の計算
-（基本教材 第3章3 文章作成）</t>
+          <t>録画・画像・名簿と費用
+基本教材 第3章3／教科書 p.100〜103・108〜115</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>録画・画像・名簿の扱いを決まりどおりに直し、確定者＋予備で費用を計算できる</t>
+          <t>録画・画像・名簿を決まりどおりに扱い、費用を計算できる。</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>録画の同意と限定公開、BCC、画像と名簿の扱いを確かめる。
-費用を計算する（確定者＋予備）。
-対応ページ（参考）: 単元23 p.100〜103、単元25 p.108〜111、単元26 p.112〜115</t>
+          <t>録画の同意と限定公開、BCC、画像と名簿の扱い。
+費用の計算（確定者＋予備）。</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3875,7 +3822,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -3885,7 +3832,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>著作権の保護期間は、教科書の「死後50年」ではなく、いまの「死後70年」で教える</t>
+          <t>著作権の保護期間は教科書の「死後50年」ではなく「死後70年」で教える</t>
         </is>
       </c>
     </row>
@@ -3898,29 +3845,28 @@
       <c r="B42" s="5" t="inlineStr">
         <is>
           <t>最終課題の予行
-（基本教材 第2章2 モデルの選び方）</t>
+基本教材 第2章2／教科書 p.12〜23</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>別の番号の材料で40分の予行をし、採点の表で自己採点できる</t>
+          <t>予行をして、採点の表で自己採点できる。</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Flash（速い）と Pro（深い）を使い分ける。
-最終課題の予行（別の番号で40分）と自己採点。
-対応ページ（参考）: 単元1〜3 p.12〜23 で全体を振り返る</t>
+          <t>Flash（速い）と Pro（深い）の使い分け。
+最終課題の予行（別の番号で40分）と自己採点。</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>練習のシート・画面録画・自己採点</t>
+          <t>最終課題の練習</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>小テスト（授業中、満点まで再提出可）</t>
+          <t>小テスト</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -3943,24 +3889,22 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>ルールどおりの人数と費用を出し、誤りだけを直したメールを、安全な共有設定で一人で仕上げられる</t>
+          <t>人数と費用を出し、誤りだけ直したメールを安全な共有で仕上げられる。</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>説明・配布10分のあと、個人作業40分。
-スマホとAIを使ってよい。
-作業中は画面を録画する</t>
+          <t>説明10分、個人作業40分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>成果物5（結果と訂正のシート・メール本文のドキュメント・画面録画）を提出フォームで提出</t>
+          <t>成果物5（提出フォーム）</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>小テストは行わない（成果物の採点で確認する）</t>
+          <t>小テストなし</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -3970,7 +3914,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>受付時間はクラスルームで設定。本人の証拠として合言葉と録画を使う</t>
+          <t>受付はクラスルームで設定。証拠は合言葉と録画</t>
         </is>
       </c>
     </row>

--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -586,10 +586,10 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>調査を作り、回答を数え、その数字から企画を決めて、SNSの投稿を作る。
-「誰に・何を・いつ・どこで」は、数字にもとづいて決める。
-日本語で調べ・数え・書くことで、日本語を使う力を高める。わからない時はAIで自分で解決する。
-AI演習（実践）・ビジネス情報リテラシーにつながる。</t>
+          <t>架空の「日本語カフェ」から「もっと留学生に来てほしい」と頼まれた設定で進める。
+アンケートを作り、集まった回答を数え、その数字で「誰に・何を・いつ・どこで」知らせるかを決める。
+決めた内容で、SNSに載せる告知画像（数枚）と紹介文を作る（実際には公開しない）。
+日本語で調べ・数え・書くことで日本語を使う力を高める。わからない時はAIで解決する。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -668,10 +668,10 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. 目的に合う形式で調査フォームを作れる。
-2. AIに作らせた式の結果を確かめ、回答を正しく数えられる。
-3. 数字から「誰に・何を・いつ・どこで」を決められる。
-4. 数字と一致するSNS投稿と投稿文を作れる。</t>
+          <t>1. 知りたいことに合うアンケートを作れる。
+2. 回答を正しく数えられる（AIに作らせた式を確かめる）。
+3. 数えた結果から、誰に・何を・いつ・どこで知らせるかを決められる。
+4. 決めた内容どおりの告知画像と紹介文を作れる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -680,13 +680,8 @@
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>採点基準は学校規定に準ずる。
-【独自の基準】
-・成果物は、課題ごとに示した条件を1つずつ○✖で見て、○の分だけ点を足す。1か所まちがえても、ほかの点は失わない。
-・本人が作った証拠（合言葉・画面録画・版の履歴など）が無い提出は0点。
-・材料の数字は学生ごとに違う。他人の答えを写しても点にならない。
-・作業時間は目安で、採点しない。受付時間はクラスルームで課題ごとに設定する。
-・小テストは満点で○。点＝20×○の数÷11（成果物の回は行わない）。欠席は✖。
-・出席率70%の学生でも、成果物で48点取ればD（60点）に届く設計にしている。</t>
+成果物は、課題ごとの条件を満たした分だけ点を足す。
+本人が作った証拠（録画など）の無い提出は0点。</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -754,8 +749,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>成果物 80点（8・12・15・20・25点）
-小テスト 20点（成果物の回を除く11回。満点まで再提出可）</t>
+          <t>成果物 80点（5回：8・12・15・20・25点）
+小テスト 20点（成果物の回以外の毎回）</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -763,8 +758,8 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>小テスト：その場で結果を返し、満点まで再提出できる。
-成果物：前の回に通し練習と自己採点。本番の後に振り返る。</t>
+          <t>小テストはその場で返し、満点まで出し直せる。
+成果物は前の回に練習し、本番の後に答え合わせをする。</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -875,7 +870,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>マーケティングとは何か
+          <t>マーケティングとは
 教科書 p.12〜15</t>
         </is>
       </c>
@@ -886,14 +881,14 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Gemini の基本操作。
-投稿の骨子（主張→理由→具体例→CTA）。
-フォームで3問を作る。</t>
+          <t>Gemini の使い方。
+告知文の組み立て（言いたいこと→理由→例→お願い）。
+アンケートで3問を作る。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>フォーム（3問）</t>
+          <t>アンケート（3問）</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -916,19 +911,19 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>ニーズとベネフィット
+          <t>お客さんが本当に欲しいもの
 教科書 p.56〜59</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>回答を正しく数え、2枚の投稿にまとめられる。</t>
+          <t>回答を数え、告知画像2枚にまとめられる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AIの答えの根拠を確かめる。
-成果物1の通し練習。</t>
+          <t>AIの答えが正しいか確かめる。
+成果物1の練習。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -956,12 +951,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>成果物1　調査から投稿まで（実技）</t>
+          <t>成果物1　アンケートから告知画像2枚（実技）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>調査から2枚の投稿を作って提出できる。</t>
+          <t>アンケートを数え、告知画像2枚を作って提出できる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -971,7 +966,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>成果物1（クラスルーム）</t>
+          <t>成果物1</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -998,20 +993,19 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>調査の方法と4P
+          <t>アンケートの作り方と数え方
 教科書 p.18〜19・48〜53・100〜101・112〜113・154</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>6形式で質問を作り、AIの式の結果を2つ以上の方法で検算できる。</t>
+          <t>質問を作り、回答を正しく数えられる。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AIに式を作らせて貼る。
-検算：①答えのわかる小さな表で試す ②範囲をなぞり画面下の合計・個数と比べる ③見当と比べる。
-重複やテスト送信を見分ける。</t>
+          <t>AIに数える式を作らせ、3つの方法で確かめる（答えのわかる小さな表で試す／合計・件数を比べる／だいたいの数と比べる）。
+同じ人の二重回答やテスト回答を除く。</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1039,20 +1033,20 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>SNSマーケティング
+          <t>SNSでの知らせ方
 教科書 p.166〜167</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>表紙の画像を作り、Canva で投稿動画にできる。</t>
+          <t>告知画像の表紙を作り、数枚の画像を動画にまとめられる。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>画像生成で表紙。
-Canva（サイズ・有料素材・MP4）。
-成果物2の通し練習。</t>
+          <t>AIで表紙の画像を作る。
+Canva で画像を並べ、動画で保存する。
+成果物2の練習。</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1080,12 +1074,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>成果物2　表紙と3ページの投稿（実技）</t>
+          <t>成果物2　表紙つきの告知画像3枚（実技）</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>表紙と3ページの投稿動画を作って提出できる。</t>
+          <t>回答を数え、表紙と画像3枚の動画を提出できる。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1095,7 +1089,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>成果物2（クラスルーム）</t>
+          <t>成果物2</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1122,19 +1116,19 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>STP・ターゲット
+          <t>誰に知らせるか（ターゲット）
 教科書 p.20〜21・66〜67・74〜81</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ターゲットを絞って人数と平均を出せる。</t>
+          <t>知らせたい人だけの人数を数えられる。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>ガイド付き学習でSTPを深める。
-AIに絞り込みの式を作らせ、数を確かめる。</t>
+          <t>お客さんを分けて、ねらう人を決める考え方。
+AIに式を作らせ、数を確かめる。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1162,19 +1156,19 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ポジショニングと競合
+          <t>競争相手を調べる
 教科書 p.90〜91・94〜95</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>地図で競合を比べ、避ける時間を決められる。</t>
+          <t>地図で近くの競争相手を比べ、重ならない時間を決められる。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>ディープリサーチで下調べ。
-表紙を3回作ってそろえる。</t>
+          <t>Googleマップで評価と口コミの数を比べる。
+表紙を3回作り、3枚ともそろえる。</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1202,12 +1196,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>成果物3　ターゲットと競合から投稿（実技）</t>
+          <t>成果物3　ねらう人を決めて告知画像5枚（実技）</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>5ページの投稿動画と表紙3枚を提出できる。</t>
+          <t>ねらう人と時間を決め、画像5枚の動画を提出できる。</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1217,7 +1211,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>成果物3（クラスルーム）</t>
+          <t>成果物3</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1244,19 +1238,19 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>検索とチャネル
+          <t>検索されている言葉を調べる
 教科書 p.124〜127・160〜161・168〜169</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>トレンドで言葉を比べ、時間帯ごとに数えられる。</t>
+          <t>Googleトレンドで言葉を比べ、多い時間帯を数えられる。</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Googleトレンド（期間・地域）。
-時刻の回答を時間帯ごとに数える（式はAIに作らせる）。</t>
+          <t>Googleトレンドの見方（期間・地域）。
+回答を時間帯ごとに数える（式はAIに作らせる）。</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1284,19 +1278,19 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>アクセス解析とKPI
+          <t>どこに・いつ出すか
 教科書 p.162〜163・174</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>投稿先を選び、グラフ入りのページと投稿文を作れる。</t>
+          <t>見られている場所を選び、グラフ入りの画像と紹介文を作れる。</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>アナリティクスのデモ（教員の画面）。
-Canva の棒グラフ、Canvas で投稿文。</t>
+          <t>アクセスの数字の見方（教員の画面で見る）。
+Canva でグラフを入れる。紹介文をAIと直す。</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1316,7 +1310,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>アナリティクスは教員の画面</t>
+          <t>アクセスの数字は教員の画面</t>
         </is>
       </c>
     </row>
@@ -1328,18 +1322,18 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>コミュニケーション・ミックス
+          <t>知らせ方の組み合わせ
 教科書 p.136〜139</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>成果物4を通して作り、自己採点できる。</t>
+          <t>成果物4を時間内に通して作れる。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>成果物4の通し練習（70分）と自己採点。</t>
+          <t>成果物4の練習と自己採点。</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1367,12 +1361,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>成果物4　3つのデータから投稿（実技）</t>
+          <t>成果物4　3つのデータから告知と紹介文（実技）</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>投稿動画と投稿文を作って提出できる。</t>
+          <t>3つのデータで決め、画像5枚と紹介文を提出できる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1382,7 +1376,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>成果物4（クラスルーム）</t>
+          <t>成果物4</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -1409,19 +1403,19 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>マーケティング・オートメーション
+          <t>決まりの例外に気をつける
 教科書 p.172〜173</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>例外の条件を考えて日付と投稿先を決められる。</t>
+          <t>祝日や載せられる枚数の上限を考えて決められる。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>連携アプリでカレンダーに予定を入れる。
-祝日・投稿の枚数上限・投稿文150字。</t>
+          <t>カレンダーに予定を入れる。
+祝日、SNSごとの枚数の上限、紹介文150字。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -1455,12 +1449,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>最終課題の形を通して作れる。</t>
+          <t>最終課題と同じ形を通して作れる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>最終課題の予行（70分）と自己採点。</t>
+          <t>最終課題の練習と自己採点。</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -1488,12 +1482,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>成果物5（最終課題）（実技）</t>
+          <t>成果物5（最終課題）　企画から告知まで（実技）</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>数字だけで企画を決め、投稿動画と投稿文を提出できる。</t>
+          <t>数字だけで企画を決め、画像5枚と紹介文を提出できる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1503,7 +1497,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>成果物5（クラスルーム）</t>
+          <t>成果物5</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">

--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -587,9 +587,9 @@
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>架空の「日本語カフェ」から「もっと留学生に来てほしい」と頼まれた設定で進める。
-アンケートを作り、集まった回答を数え、その数字で「誰に・何を・いつ・どこで」知らせるかを決める。
-決めた内容で、SNSに載せる告知画像（数枚）と紹介文を作る（実際には公開しない）。
-日本語で調べ・数え・書くことで日本語を使う力を高める。わからない時はAIで解決する。</t>
+Googleフォームでアンケートを作り、回答をスプレッドシートで集計し、その数字で「誰に・何を・いつ・どこで」告知するかを決める。
+決めた内容で、SNS用のカルーセル（Canvaで作る数ページの画像。MP4で提出）と投稿文を作る。実際には公開しない。
+わからない時はGeminiで自分で解決し、出てきた答えや式は必ず確かめる。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -668,10 +668,10 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. 知りたいことに合うアンケートを作れる。
-2. 回答を正しく数えられる（AIに作らせた式を確かめる）。
-3. 数えた結果から、誰に・何を・いつ・どこで知らせるかを決められる。
-4. 決めた内容どおりの告知画像と紹介文を作れる。</t>
+          <t>1. 目的に合う形式でGoogleフォームのアンケートを作れる。
+2. 回答をスプレッドシートで正しく集計できる（Geminiが作った式を検算する）。
+3. 集計結果から、ターゲット・内容・日時・投稿先を決められる。
+4. 決めた内容どおりのカルーセルと投稿文を作れる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -870,25 +870,25 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>マーケティングとは
+          <t>セリングとマーケティング
 教科書 p.12〜15</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>売ることとマーケティングの違いを説明できる。</t>
+          <t>セリングとマーケティングの違いを説明し、Googleフォームで3形式の質問を作成できる。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Gemini の使い方。
-告知文の組み立て（言いたいこと→理由→例→お願い）。
-アンケートで3問を作る。</t>
+          <t>Geminiの基本操作。
+投稿文の型（主張→理由→具体例→CTA）。
+Googleフォームで3問を作る。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>アンケート（3問）</t>
+          <t>Googleフォーム（3問）</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -911,19 +911,19 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>お客さんが本当に欲しいもの
+          <t>ニーズとベネフィット
 教科書 p.56〜59</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>回答を数え、告知画像2枚にまとめられる。</t>
+          <t>フォームの回答をスプレッドシートで集計し（テスト送信を除く）、Googleスライド2枚にまとめられる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AIの答えが正しいか確かめる。
-成果物1の練習。</t>
+          <t>Geminiの回答の根拠を確かめる。
+成果物1の通し練習（スプレッドシートで集計→スライド2枚）。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>成果物1　アンケートから告知画像2枚（実技）</t>
+          <t>成果物1　アンケートからスライド2枚（実技）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>アンケートを数え、告知画像2枚を作って提出できる。</t>
+          <t>3問のアンケート結果を集計し、最多の回答をもとにGoogleスライド2枚の告知を作成して提出できる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -993,19 +993,20 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>アンケートの作り方と数え方
+          <t>リサーチの方法・4P・AISAS
 教科書 p.18〜19・48〜53・100〜101・112〜113・154</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>質問を作り、回答を正しく数えられる。</t>
+          <t>Googleフォームで6形式の質問を作成し、重複回答を除いて割合を集計できる（Geminiの式を検算する）。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AIに数える式を作らせ、3つの方法で確かめる（答えのわかる小さな表で試す／合計・件数を比べる／だいたいの数と比べる）。
-同じ人の二重回答やテスト回答を除く。</t>
+          <t>Googleフォームの6形式。
+Geminiに集計の式を作らせ、3つの方法で検算（答えのわかる小さな表で試す／範囲を選んで合計・件数を比べる／概算と比べる）。
+重複回答・テスト送信を除く。</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1033,20 +1034,20 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>SNSでの知らせ方
+          <t>SNSマーケティング
 教科書 p.166〜167</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>告知画像の表紙を作り、数枚の画像を動画にまとめられる。</t>
+          <t>Geminiで表紙画像を生成し、Canvaで3ページのカルーセルを作ってMP4で書き出せる。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AIで表紙の画像を作る。
-Canva で画像を並べ、動画で保存する。
-成果物2の練習。</t>
+          <t>Geminiで表紙画像を生成。
+Canvaでカルーセルを作りMP4で書き出す（サイズ・有料素材の見分け方）。
+成果物2の通し練習。</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1074,12 +1075,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>成果物2　表紙つきの告知画像3枚（実技）</t>
+          <t>成果物2　表紙＋3ページのカルーセル（実技）</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>回答を数え、表紙と画像3枚の動画を提出できる。</t>
+          <t>アンケートを集計し、その数字を載せた表紙＋3ページのカルーセル動画（Canva）を作成して提出できる。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1116,19 +1117,19 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>誰に知らせるか（ターゲット）
+          <t>STP・ペルソナ
 教科書 p.20〜21・66〜67・74〜81</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>知らせたい人だけの人数を数えられる。</t>
+          <t>STPの考え方でターゲットを決め、その回答だけを抽出して人数と満足度の平均を集計できる。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>お客さんを分けて、ねらう人を決める考え方。
-AIに式を作らせ、数を確かめる。</t>
+          <t>Geminiのガイド付き学習でSTPを整理。
+ターゲットの回答だけを抽出して集計（式はGeminiに作らせ検算）。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1156,19 +1157,19 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>競争相手を調べる
+          <t>ポジショニングと競合
 教科書 p.90〜91・94〜95</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>地図で近くの競争相手を比べ、重ならない時間を決められる。</t>
+          <t>Googleマップで近くの競合の評価と口コミ件数を比べ、競合と重ならない開催時間を決められる。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Googleマップで評価と口コミの数を比べる。
-表紙を3回作り、3枚ともそろえる。</t>
+          <t>Googleマップで競合の評価と口コミ件数を比較。
+Geminiで同じ条件の表紙を3回生成し、3枚ともそろえる。</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1196,12 +1197,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>成果物3　ねらう人を決めて告知画像5枚（実技）</t>
+          <t>成果物3　ターゲットと競合から5ページのカルーセル（実技）</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ねらう人と時間を決め、画像5枚の動画を提出できる。</t>
+          <t>ターゲットと開催時間を決め、5ページのカルーセル動画と、同じ条件で生成した表紙3枚を提出できる。</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1238,19 +1239,19 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>検索されている言葉を調べる
+          <t>SEO・AEO・流通チャネル
 教科書 p.124〜127・160〜161・168〜169</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Googleトレンドで言葉を比べ、多い時間帯を数えられる。</t>
+          <t>Googleトレンドで検索キーワードを比較し、アンケートの回答時刻を時間帯別に集計できる。</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Googleトレンドの見方（期間・地域）。
-回答を時間帯ごとに数える（式はAIに作らせる）。</t>
+          <t>Googleトレンドで検索キーワードを比較（期間・地域）。
+回答時刻を時間帯別に集計。</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1278,19 +1279,19 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>どこに・いつ出すか
+          <t>アクセス解析とKPI
 教科書 p.162〜163・174</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>見られている場所を選び、グラフ入りの画像と紹介文を作れる。</t>
+          <t>GA4のデモでユーザー数を読み取って投稿先のSNSを選び、棒グラフ入りのカルーセルと投稿文（100字）を作成できる。</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>アクセスの数字の見方（教員の画面で見る）。
-Canva でグラフを入れる。紹介文をAIと直す。</t>
+          <t>GA4のデモ（教員の画面）でユーザー数を読む。
+Canvaで棒グラフ入りのページを作り、投稿文をGeminiのCanvasで直す。</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1310,7 +1311,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>アクセスの数字は教員の画面</t>
+          <t>GA4は教員の画面で見せる</t>
         </is>
       </c>
     </row>
@@ -1322,18 +1323,18 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>知らせ方の組み合わせ
+          <t>コミュニケーション・ミックス
 教科書 p.136〜139</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>成果物4を時間内に通して作れる。</t>
+          <t>成果物4の通し練習を70分で最後まで行い、採点表で自己採点できる。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>成果物4の練習と自己採点。</t>
+          <t>成果物4の通し練習（70分）と自己採点。</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1361,12 +1362,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>成果物4　3つのデータから告知と紹介文（実技）</t>
+          <t>成果物4　3つのデータからカルーセルと投稿文（実技）</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>3つのデータで決め、画像5枚と紹介文を提出できる。</t>
+          <t>アンケート・Googleトレンド・GA4の3つのデータから投稿先と日時を決め、カルーセル動画と投稿文（100字）を提出できる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1403,19 +1404,19 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>決まりの例外に気をつける
+          <t>マーケティング・オートメーション
 教科書 p.172〜173</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>祝日や載せられる枚数の上限を考えて決められる。</t>
+          <t>祝日やSNSごとの枚数上限（Xは4枚まで）を考えて開催日と投稿先を決め、投稿文（150字）を作成できる。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>カレンダーに予定を入れる。
-祝日、SNSごとの枚数の上限、紹介文150字。</t>
+          <t>Geminiの連携アプリでGoogleカレンダーに予定を入れる。
+祝日・SNSごとの枚数上限（Xは4枚）・投稿文150字。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -1443,18 +1444,18 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>全体の振り返り
+          <t>マーケティングの5段階（振り返り）
 教科書 p.22〜25</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>最終課題と同じ形を通して作れる。</t>
+          <t>最終課題の予行を別のデータで70分行い、自己採点できる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>最終課題の練習と自己採点。</t>
+          <t>最終課題の予行（別のデータで70分）と自己採点。</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -1482,12 +1483,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>成果物5（最終課題）　企画から告知まで（実技）</t>
+          <t>成果物5（最終課題）　アンケートからカルーセルと投稿文（実技）</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>数字だけで企画を決め、画像5枚と紹介文を提出できる。</t>
+          <t>12問のアンケート集計だけから「誰に・何を・いつ・どこで」を決め、カルーセル動画と投稿文（150字）を提出できる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">

--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -1676,10 +1676,10 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>日本語で書かれたルールを読み、張り紙・スライド・表・画像を作る。
-AIの答えはそのまま使わず、原文と比べて誤りを自分で直す。
-依頼を受けてから届けるまでを一人で行う。回が進むと材料と条件が増える。
-わからない時はAIで自分で解決する。マーケティング・ビジネス情報リテラシーにつながる。</t>
+          <t>架空の学校の図書室や事務室から「利用ルールの張り紙を作り、利用記録を集計してほしい」と頼まれた設定で進める。
+先輩がAIで作った下書きをルールの原文だけを正として直し、張り紙（Googleドキュメント）・Googleスライド・集計表（スプレッドシート）・画像の4つを作る。
+作ったものは共有設定とGoogleフォームで提出する。回が進むとGmailでの納品やGoogleカレンダーの招待が加わる。
+わからない時はGeminiで自分で解決し、出てきた答えや式は必ず確かめる。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -1688,9 +1688,9 @@
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>基本教材：Geminiビジネス活用ガイド（最新の機能で扱う）
-教員が作った材料（ルールの原文・AIの下書き・利用記録）を毎回配る
+材料：教員が作ったルールの原文・AIの下書き・利用記録を毎回配る
 環境：スマホ、個人の Google アカウント（無料）
-ツール：Gemini、Gemini Notebook、画像生成、スプレッドシート、スライド、ドキュメント、ドライブ、Gmail、カレンダー、Meet、クラスルーム</t>
+ツール：Gemini、Gemini Notebook、ドキュメント、スライド、スプレッドシート、ドライブ、フォト、フォーム、Gmail、カレンダー、Meet</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -1758,10 +1758,10 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. 原文だけを正として、AIの下書きの誤りを直せる。
-2. AIに作らせた式の結果を確かめ、集計表を作れる。
-3. 条件を守った画像を3枚そろえ、約束どおりのスライドを作れる。
-4. 作ったものをメール・共有・予定の招待で届けられる。</t>
+          <t>1. ルールの原文だけを正として、AIの下書きの誤りを直した張り紙と誤り一覧を作成できる。
+2. Geminiに作らせた式を検算し、行を足しても正しく動く集計表をスプレッドシートで作成できる。
+3. 条件を守った画像を3枚そろえ、約束どおりの形のGoogleスライドを作成できる。
+4. 作ったものを共有設定・Gmail・Googleカレンダーの招待で届けられる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1770,13 +1770,8 @@
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>採点基準は学校規定に準ずる。
-【独自の基準】
-・成果物は、課題ごとに示した条件を1つずつ○✖で見て、○の分だけ点を足す。1か所まちがえても、ほかの点は失わない。
-・本人が作った証拠（合言葉・画面録画・版の履歴など）が無い提出は0点。
-・材料の数字は学生ごとに違う。他人の答えを写しても点にならない。
-・作業時間は目安で、採点しない。受付時間はクラスルームで課題ごとに設定する。
-・小テストは満点で○。点＝20×○の数÷13（成果物の回は行わない）。欠席は✖。
-・出席率70%の学生でも、成果物で48点取ればD（60点）に届く設計にしている。</t>
+成果物は、課題ごとの条件を満たした分だけ点を足す。
+本人が作った証拠（録画など）の無い提出は0点。</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -1844,8 +1839,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>成果物 80点（8・12・15・20・25点）
-小テスト 20点（成果物の回を除く13回。満点まで再提出可）</t>
+          <t>成果物 80点（5回：8・12・15・20・25点）
+小テスト 20点（成果物の回以外の毎回）</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1853,8 +1848,8 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>小テスト：その場で結果を返し、満点まで再提出できる。
-成果物：本番の次の回に答え合わせをする（5・9・13・16回）。</t>
+          <t>小テストはその場で返し、満点まで出し直せる。
+成果物は前の回に練習し、本番の後に答え合わせをする。</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -1965,20 +1960,20 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ガイダンス・ファイルの提出
+          <t>ガイダンス・共有と提出
 基本教材 2章1</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>作ったファイルを教員に届く形で提出できる。</t>
+          <t>ファイル名に合言葉を入れ、教員を編集者として共有し、Googleフォームで提出できる。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>科目の進め方と評価。
-ファイル名と合言葉、教員への共有。
-Gemini Notebook に文章を貼る。</t>
+          <t>科目の進め方と評価。Geminiの基本操作。
+Googleドライブのファイル名と合言葉、共有設定（閲覧者/編集者）。
+Gemini Notebookに文章を貼る。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2006,19 +2001,20 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>原文を正として張り紙を直す
+          <t>原文と照合して張り紙を直す
 基本教材 5章1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>原文だけを正として下書きを直せる。</t>
+          <t>Gemini Notebookで原文との照合表を作成し、下書きの誤りをGoogleドキュメントで直せる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Gemini Notebook で原文だけを根拠に答えさせる。
-照合表を作り、張り紙を直す。</t>
+          <t>Gemini Notebookで原文だけを根拠に答えさせる。
+照合表を作り、実在する語の誤字を探す。
+Googleドキュメントで張り紙を直す。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2046,19 +2042,19 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>式で数える・画像の画風
+          <t>式で数える・画風を変える
 基本教材 3章5・2章6</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AIの式で数え、保つ点を守って画像を作れる。</t>
+          <t>Geminiの式で遅れの回数を数えて検算し、画風を変えた画像とGoogleスライド1枚を作成できる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AIに式を作らせ、結果を確かめる。
-画像生成で画風を変える。スライド1枚。
+          <t>Geminiに式を作らせ、スプレッドシートで検算。
+画像生成で画風を変え、保つ点を守る。
 成果物1の通し練習（30分）。</t>
         </is>
       </c>
@@ -2087,12 +2083,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>成果物1　4つを一人で通す（実技）</t>
+          <t>成果物1　タブレット貸出しの張り紙一式（実技）</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>張り紙・スライド・集計表・画像を作って提出できる。</t>
+          <t>図書室の貸出しルールをもとに、張り紙・スライド1枚・集計表・画像を作成して提出できる。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2102,7 +2098,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>成果物1（クラスルーム）</t>
+          <t>成果物1</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2117,7 +2113,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -2135,13 +2131,14 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>下書きの誤りを数を知らされずに探し切れる。</t>
+          <t>Gemini Notebookで照合表を作成し、意味が違う誤字まで数を知らされずに探し切れる。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
           <t>成果物1の答え合わせ。
-6件の照合、意味が違う誤字の練習。</t>
+Gemini Notebookで6件を照合。
+読めるのに意味が違う誤字を探す。</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2175,13 +2172,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>出力を約束どおりの形に直し、上限ちょうどを正しく数えられる。</t>
+          <t>形の約束どおりのGoogleスライドを作成し、上限ちょうどを違反にしない式を検算できる。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>出力の形を指示して文章を作る。
-「上限ちょうどは違反でない」式をAIに作らせ、確かめる。</t>
+          <t>Geminiに出力の形を指定する（枚数・右下の番号・括弧）。
+「上限ちょうどは違反でない」式をGeminiに作らせ、検算する。</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2215,12 +2212,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>同じ条件の画像を3枚そろえ、1枚ずつ確かめられる。</t>
+          <t>同じ指示で画像を3枚生成し、保つ点（数・色・位置・比率）を1枚ずつ確かめられる。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>同じ指示で3枚作り、保つ点を確かめる。
+          <t>同じ指示で3枚生成し、保つ点を1枚ずつ○✖で確かめる。
 成果物2の通し練習（40分）。</t>
         </is>
       </c>
@@ -2249,12 +2246,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>成果物2　条件の増えた一連の仕事（実技）</t>
+          <t>成果物2　グループ学習室の張り紙一式（実技）</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>誤りを直し、スライド・集計表・画像3枚を提出できる。</t>
+          <t>下書きの誤り6件を直し、張り紙・スライド2枚・集計表・画像3枚を作成して提出できる。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2264,7 +2261,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>成果物2（クラスルーム）</t>
+          <t>成果物2</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2279,7 +2276,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -2291,19 +2288,20 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>古い値と逆の文を見抜く
+          <t>旧版の値と原文と逆の文
 基本教材 3章3</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>旧版の値と原文と逆の文を見抜き、誤り一覧を作れる。</t>
+          <t>改定の記録から旧版の値と原文と逆の文を見抜き、誤り一覧をスプレッドシートで作成できる。</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
           <t>成果物2の答え合わせ。
-改定の記録を読み、誤り一覧を作る。</t>
+改定の記録を読み、旧版の値・原文と逆の追加を探す。
+誤り一覧（どの文・どう違う・正しい内容）を作る。</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2331,19 +2329,19 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>行を足しても正しい表
+          <t>行を足しても正しい集計表
 基本教材 3章5</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>延長と停止の開始日を出し、行を足して確かめられる。</t>
+          <t>延長と予約停止の開始日を出す式を作成し、行を足して正しく変わるか検算できる。</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>開始日の式をAIに作らせる。
-行を足して結果が正しく変わるか確かめる。</t>
+          <t>延長・停止開始日（3回目の翌日）の式をGeminiに作らせる。
+自分で行を足し、結果が正しく変わるか確かめる。</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2371,19 +2369,19 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>メールで納品する
+          <t>Gmailで納品する
 基本教材 3章3</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>集計の結果をメールに正しく書き、納品できる。</t>
+          <t>Geminiで納品メールを下書きし、集計の結果を本文に入れてGmailで送信できる。</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>スライド3枚、画像から物を消す。
-Gemini で下書きし、Gmail で送る。
+          <t>Googleスライド3枚。画像から物を消す。
+Geminiで納品メールを下書きし、Gmailで送る（件名の約束）。
 成果物3の通し練習（50分）。</t>
         </is>
       </c>
@@ -2412,12 +2410,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>成果物3　メールで納品する（実技）</t>
+          <t>成果物3　面接練習室の張り紙一式と納品メール（実技）</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>誤り一覧・集計表・画像3枚をそろえ、メールで納品できる。</t>
+          <t>下書きの誤り9件を直し、張り紙・スライド3枚・集計表・誤り一覧・画像3枚をGmailで納品できる。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2427,7 +2425,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>成果物3（クラスルーム）</t>
+          <t>成果物3</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2442,7 +2440,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -2460,13 +2458,14 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>書かれていないこと・重複・詰め込みを直せる。</t>
+          <t>AIが作った詰め込みすぎのGoogleスライドを、GeminiのCanvasで1枚1つの話に作り直せる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
           <t>成果物3の答え合わせ。
-Canvas で1枚1つの話に作り直す。</t>
+元のスライドを原文と照合し、脱落・重複を直す。
+Canvasで作り直し、同じ頼み方で2枚を再現する。</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2500,13 +2499,14 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>集計・グラフ・報告の数字をそろえ、説明会に招待できる。</t>
+          <t>月で数え直す集計表とグラフを作成し、Google Meet付きの予定をGoogleカレンダーで作って招待できる。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>月で数え直す式とグラフをAIと作る。画像に文字を入れる。
-カレンダーに Meet つきの予定を作り招待する。</t>
+          <t>月で数え直す式と部屋別件数のグラフ。画像に文字を入れる。
+Geminiの連携アプリでGoogleカレンダー・Keepに予定を入れる。
+Meetを付けて教員を招待する。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>成果物4　最終課題に近い一連の仕事（実技）</t>
+          <t>成果物4　撮影ブースの説明会の準備一式（実技）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>スライド・集計表・画像3枚・納品メール・招待を提出できる。</t>
+          <t>元のスライド8枚を作り直し、集計表・画像3枚・納品メール・Google Meet付きの招待を作成して提出できる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>成果物4（クラスルーム）</t>
+          <t>成果物4</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。本人の証拠は合言葉と作成時刻</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -2586,13 +2586,14 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>期間で条件が変わる集計と誤り一覧を作れる。</t>
+          <t>期間で上限が変わる式を作成し、Gemini Notebookで条番号つきの誤り一覧を作れる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
           <t>成果物4の答え合わせ。
-Flash と Pro の使い分け。</t>
+FlashとProの使い分け（速さと正確さ）。
+条番号つきの誤り一覧、期間で上限が変わる式。</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2626,12 +2627,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>4つを時間内に仕上げ、画面録画つきで提出できる。</t>
+          <t>最終課題の練習版を画面録画しながら60分で仕上げ、Googleフォームで提出できる。</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>ガイド付き学習で自分の誤りを振り返る。
+          <t>Geminiの学習モードで自分の誤りを振り返る。
 最終課題の通し練習（60分、画面録画）。</t>
         </is>
       </c>
@@ -2660,22 +2661,22 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>成果物5　4つを誤りゼロで仕上げる（実技）</t>
+          <t>成果物5（最終課題）　充電ロッカーの張り紙一式（実技）</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>原文だけを正として4つを誤りなく仕上げられる。</t>
+          <t>原文だけを正として、張り紙・スライド3枚・集計表と誤り一覧・画像3枚を作成して提出できる。</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>説明10分、個人作業90分。スマホ・AI使用可。作業中は画面録画。</t>
+          <t>説明10分、個人作業90分。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>成果物5（クラスルーム）</t>
+          <t>成果物5</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2690,7 +2691,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。本人の証拠は合言葉と画面録画（リンクは次の授業の開始まで）</t>
+          <t>受付はクラスルームで設定。作業中は画面録画（リンクは次の授業の開始まで）</t>
         </is>
       </c>
     </row>
@@ -2853,10 +2854,10 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>仕事のルール・メール・申込データを日本語で読み、連絡と記録を正しく行う。
-架空の学内講座の運営を一人（成果物2は2人1組）で行い、回ごとに材料と条件が増える。
-扱うのはメールの宛先、共有の設定、個人情報・著作権、データの数え方。わからない時はAIで自分で解決し、ルールと照らして確かめる。
-マーケティング・AI演習（実践）につながり、この科目は「運用する力」を担う。</t>
+          <t>架空の学内講座の運営を、前任者から引き継いだ設定で進める。
+届いたメール・運営のルール・申込データを読み、Gmailで日程確定や補欠のお知らせを送り、Google Meetで運営会議を開いて議事録とToDoを作る。
+Googleドライブの共有フォルダを整理して共有設定を直し、スプレッドシートで申込を数えて確定・補欠・費用を出す。成果物は5回（成果物2は2人1組）で、画面録画などを添えてGoogleフォームで提出する。
+わからない時はGeminiで自分で解決し、答えは運営のルールと照らして確かめる。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -2864,11 +2865,10 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>教科書：『留学生のためのITリテラシー』（参考。対応ページを授業計画に示す）
+          <t>教科書：『留学生のためのITリテラシー』（対応ページを授業計画に示す）
 基本教材：Geminiビジネス活用ガイド（最新の機能で扱う）
-配布：運営のルール、メール、申込データ、前任者の下書き
-環境：スマホ、個人の Google アカウント（無料）
-ツール：Gemini、Gemini Notebook、Gmail、カレンダー、Meet、Keep、ドキュメント、ドライブ、スプレッドシート、フォーム、フォト、YouTube、画面録画、Classroom</t>
+環境：スマホ、個人の Google アカウント（無料）。配布：運営のルール、メール、申込データ、前任者の下書き
+ツール：Gemini、Gemini Notebook、Gmail、Googleカレンダー、Google Meet、Keep、Googleドキュメント、Googleドライブ、スプレッドシート、Googleフォーム、Googleフォト、YouTube、画面録画</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -2936,10 +2936,10 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. メールから最新の決定を拾い、下書きの誤りだけを直して、正しい宛先（BCC など）で送れる。
-2. 会議を開き、議事録と ToDo の期限をルールどおりに作れる。
-3. 共有フォルダを整理し、共有の設定を安全に直せる。
-4. AIに作らせた式の結果を確かめ、申込を数えて確定と補欠を決められる。</t>
+          <t>1. メールから最新の決定を拾い、下書きの誤りだけを直して、GmailでBCCなど正しい宛先で送れる。
+2. Google Meetで会議を開き、Googleドキュメントで議事録を作成し、ToDoの期限をGoogleカレンダーに入れられる。
+3. Googleドライブの共有フォルダを整理し、共有設定（リンク公開、閲覧者・編集者）を安全に直せる。
+4. Geminiが作った式をスプレッドシートで検算し、申込を数えて確定・補欠と費用を出せる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -2948,13 +2948,8 @@
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>採点基準は学校規定に準ずる。
-【独自の基準】
-・成果物は、課題ごとに示した条件を1つずつ○✖で見て、○の分だけ点を足す。1か所まちがえても、ほかの点は失わない。
-・本人が作った証拠（合言葉・画面録画・版の履歴など）が無い提出は0点。
-・材料の数字は学生ごとに違う。他人の答えを写しても点にならない。
-・作業時間は目安で、採点しない。受付時間はクラスルームで課題ごとに設定する。
-・小テストは満点で○。点＝20×○の数÷14（成果物の回は行わない）。欠席は✖。
-・出席率70%の学生でも、成果物で48点取ればD（60点）に届く設計にしている。</t>
+成果物は、課題ごとの条件を満たした分だけ点を足す。
+本人が作った証拠（録画など）の無い提出は0点。</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -3022,8 +3017,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>成果物 80点（8・12・15・20・25点）
-小テスト 20点（成果物の回を除く14回。授業中のみ、満点まで再提出可）</t>
+          <t>成果物 80点（5回：8・12・15・20・25点）
+小テスト 20点（成果物の回以外の毎回）</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -3031,8 +3026,8 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>小テスト：その場で結果を返し、満点まで再提出できる。
-成果物：前の回に別の番号の材料で通し練習（14・18回は自己採点も）。成果物1は本番の回で答え合わせ。採点の後に振り返る。</t>
+          <t>小テストはその場で返し、満点まで出し直せる。
+成果物は前の回に練習し、本番の後に答え合わせをする。</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -3149,19 +3144,19 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>To・CC・BCC を使い分けて送り、曜日を確かめられる。</t>
+          <t>GmailでTo・CC・BCCを使い分けてメールを送り、Googleカレンダーで日付の曜日を確かめられる。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>科目の進め方と評価。
-Gmail の To・CC・BCC、カレンダーで曜日の確認。
-提出フォームの練習。</t>
+          <t>科目の進め方と評価。Geminiの基本操作。
+GmailのTo・CC・BCC、Googleカレンダーで曜日の確認。
+Googleフォームで提出の練習。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>練習の提出</t>
+          <t>提出の練習</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -3190,12 +3185,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>最新の合意を拾い、正しい宛先で確定のメールを送れる。</t>
+          <t>メールのやり取りから最新の日時・会場を拾い、Geminiが作った返信の下書きを直してGmailで送れる。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AIに返信の下書きを作らせ、決まりと照らして直す。
+          <t>Geminiに返信の下書きを作らせ、運営のルールと照らして直す。
 成果物1の通し練習（別の番号の材料）。</t>
         </is>
       </c>
@@ -3224,12 +3219,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>成果物1　日程変更への返信（実技）</t>
+          <t>成果物1　日程確定のメール（実技）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>最新の日時・会場を拾い、BCC で確定のメールを送れる。</t>
+          <t>4通のメールから最新の日時・会場を拾って曜日を確かめ、GmailのBCCで日程確定のメールを送り、Googleフォームで提出できる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -3239,7 +3234,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>成果物1（提出フォーム）</t>
+          <t>成果物1</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -3254,7 +3249,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。証拠はメールの差出人と提出フォームのアドレスの照合</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>
@@ -3272,13 +3267,13 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>カレンダーから招待して Meet を開き、チャットで話し合える。</t>
+          <t>GoogleカレンダーからGoogle Meetの会議に招待し、チャットで話し合ってKeepのチェックリストで分担できる。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>カレンダーから招待し、Meet のチャットで話す。
-Keep のチェックリストで分担。Gemini の履歴と名前の変更。</t>
+          <t>GoogleカレンダーからMeetに招待し、Meetのチャットで話す。
+Keepのチェックリストで分担。Geminiのチャット履歴と名前の変更。</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3306,19 +3301,19 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>議事録と ToDo の期限
+          <t>議事録とToDoの期限
 基本教材 第3章3／教科書 p.88〜91・104〜107</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>議事録を作り、ToDo の期限を決まりどおりに出せる。</t>
+          <t>Googleドキュメントで議事録を作成し、ToDoの期限を決まり（営業日・曜日）どおりに計算できる。</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AIで議事録の型を作り、話していないことが足されていないか確かめる。
-期限の計算（営業日・曜日）。</t>
+          <t>Geminiで議事録の型を作り、話していないことが足されていないか確かめる。
+ToDoの期限の計算（営業日・曜日）。</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3352,12 +3347,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>議事録の要点を出させ、元と照らして確かめられる。</t>
+          <t>Gemini Notebookに議事録を入れて要点を出させ、元の議事録と照らして確かめられる。</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Gemini Notebook で議事録の要点を出させ、元と照らす。
+          <t>Gemini Notebookで議事録の要点を出させ、元と照らす。
 成果物2の通し練習（2人1組、短い版）。</t>
         </is>
       </c>
@@ -3386,23 +3381,22 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>成果物2　運営会議（実技・2人1組）</t>
+          <t>成果物2　運営会議の議事録とToDo（実技・2人1組）</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>会議を開き、議事録を正しい宛先で送り、ToDo を期限どおりに入れられる。</t>
+          <t>Google Meetで会議を開き、Googleドキュメントの議事録をGmailで相手に送り、ToDoの期限をGoogleカレンダーに入れて提出できる。</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>説明10分、2人1組で作業し開始から85分を目安に提出。スマホ・AI使用可。
-会議は Meet のチャットで2回（各15分）。</t>
+          <t>説明10分、2人1組で作業85分（Meetのチャットで会議2回、各15分）。スマホ・AI使用可。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>成果物2（提出フォーム）</t>
+          <t>成果物2</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -3417,7 +3411,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。証拠は合言葉と版の履歴。奇数の時は1組だけ3人</t>
+          <t>受付はクラスルームで設定。奇数の時は1組だけ3人</t>
         </is>
       </c>
     </row>
@@ -3435,12 +3429,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>中身の日付で最新版を見分け、決まりどおりに整理できる。</t>
+          <t>Googleドライブで中身の日付から最新版を見分け、名前の変更・フォルダ作成・移動で決まりどおりに整理できる。</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>ドライブで名前の変更・フォルダ作成・移動。
+          <t>Googleドライブで名前の変更・フォルダ作成・移動。
 中身の日付で最新版を見分ける。</t>
         </is>
       </c>
@@ -3475,14 +3469,14 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>リンク公開を止め、閲覧者・編集者を正しく設定できる。</t>
+          <t>Googleドライブのリンク公開を止めて閲覧者・編集者を正しく設定し、Googleフォトのアルバムを必要な人だけに共有できる。</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AIに写り込みと撮影場所の確かめ方を聞く。
-共有の設定（リンク公開、閲覧者・編集者、学外への名簿）。
-フォトのアルバムと切り取り。</t>
+          <t>Geminiに写り込みと撮影場所の確かめ方を聞く。
+共有設定（リンク公開、閲覧者・編集者、学外への名簿）。
+Googleフォトのアルバムと切り取り。</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -3516,13 +3510,13 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>空白・取消・申し込み直し・締切後を正しく扱い、人数を出せる。</t>
+          <t>Geminiが作った式でスプレッドシートの申込を数え（空白・取消・申し込み直し・締切後）、3つの方法で検算できる。</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AIに式を作らせて貼る。
-検算：①答えのわかる小さな表で試す ②範囲をなぞり画面下の合計・個数と比べる ③見当と比べる。
+          <t>Geminiに式を作らせてスプレッドシートに貼る。
+検算：答えのわかる小さな表で試す／範囲をなぞり画面下の合計・個数と比べる／見当と比べる。
 画面録画をして成果物3の通し練習。</t>
         </is>
       </c>
@@ -3556,7 +3550,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>フォルダを整理して危ない共有を止め、人数をメールで報告できる。</t>
+          <t>Googleドライブの共有フォルダを整理して危ない共有を止め、スプレッドシートで出した人数をGmailで報告し、画面録画を添えて提出できる。</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -3566,7 +3560,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>成果物3（提出フォーム）</t>
+          <t>成果物3</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -3581,7 +3575,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。証拠は合言葉と録画。録画は次の授業の開始まで可</t>
+          <t>受付はクラスルームで設定。録画は次の授業の開始まで可</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3593,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>最新の回答だけを残し、定員で確定と補欠に分けられる。</t>
+          <t>スプレッドシートで最新の回答だけを残して時刻順に並べ、定員で確定と補欠に分けられる。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AIに式を作らせ、最新の回答だけを残して時刻順に並べる。
+          <t>Geminiに式を作らせ、最新の回答だけを残して時刻順に並べる。
 定員を超えた人を補欠にする。</t>
         </is>
       </c>
@@ -3639,12 +3633,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>下書きの誤りだけを直し、データを変えても式が正しいか確かめられる。</t>
+          <t>Googleドキュメントの下書きの誤りだけを直し、データを差し替えても式の結果が正しいか確かめられる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AIの直しを決まりと照らして選ぶ（直しすぎない）。
+          <t>Geminiの直しを運営のルールと照らして選ぶ（直しすぎない）。
 データを差し替えて式の結果を確かめる。</t>
         </is>
       </c>
@@ -3679,13 +3673,13 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>通し練習をして、採点の表で自分の誤りを見つけられる。</t>
+          <t>成果物4の通し練習を40分で行い、採点表で自己採点して自分の誤りを見つけられる。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
           <t>成果物4の通し練習（40分）と自己採点。
-ガイド付き学習で誤りを振り返る。</t>
+Geminiのガイド付き学習で誤りを振り返る。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3713,12 +3707,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>成果物4　補欠の決定とお知らせ（実技）</t>
+          <t>成果物4　補欠の決定とお知らせメール（実技）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>補欠を決め、下書きを直して補欠の方に BCC で予約送信できる。</t>
+          <t>申込データから確定と補欠を決め、下書きを直したお知らせをGmailのBCCで予約送信し、画面録画を添えて提出できる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3728,7 +3722,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>成果物4（提出フォーム）</t>
+          <t>成果物4</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3743,7 +3737,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。証拠は合言葉と録画（YouTube 限定公開）。録画は次の授業の開始まで可</t>
+          <t>受付はクラスルームで設定。録画はYouTube限定公開、次の授業の開始まで可</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3755,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>改定後のルールで、表記ゆれをそろえて数えられる。</t>
+          <t>Gemini Notebookで改定後のルールを確かめ、表記ゆれ（全角・古い選択肢）をそろえて申込を数えられる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Gemini Notebook にルールを入れ、根拠つきで答えさせる。
+          <t>Gemini Notebookにルールを入れ、根拠つきで答えさせる。
 表記ゆれ（全角・古い選択肢）をそろえて数える。</t>
         </is>
       </c>
@@ -3801,7 +3795,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>録画・画像・名簿を決まりどおりに扱い、費用を計算できる。</t>
+          <t>録画・画像・名簿を決まりどおりに扱う文面に直し、印刷費（確定者＋予備）を計算できる。</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3845,12 +3839,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>予行をして、採点の表で自己採点できる。</t>
+          <t>最終課題の予行を別の番号の材料で40分行い、自己採点できる。</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Flash（速い）と Pro（深い）の使い分け。
+          <t>GeminiのFlash（速い）とPro（深い）の使い分け。
 最終課題の予行（別の番号で40分）と自己採点。</t>
         </is>
       </c>
@@ -3879,12 +3873,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>成果物5　講座運用の引き継ぎ（実技・最終課題）</t>
+          <t>成果物5　講座運営の引き継ぎ（実技・最終課題）</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>人数と費用を出し、誤りだけ直したメールを安全な共有で仕上げられる。</t>
+          <t>申込データから人数と印刷費を出し、前任者のメールの誤りだけを直して安全な共有設定で仕上げ、画面録画を添えて提出できる。</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3894,7 +3888,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>成果物5（提出フォーム）</t>
+          <t>成果物5</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3909,7 +3903,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>受付はクラスルームで設定。証拠は合言葉と録画</t>
+          <t>受付はクラスルームで設定</t>
         </is>
       </c>
     </row>

--- a/docs/drafts/syllabus-sheets/syllabus.xlsx
+++ b/docs/drafts/syllabus-sheets/syllabus.xlsx
@@ -586,10 +586,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>架空の「日本語カフェ」から「もっと留学生に来てほしい」と頼まれた設定で進める。
-Googleフォームでアンケートを作り、回答をスプレッドシートで集計し、その数字で「誰に・何を・いつ・どこで」告知するかを決める。
-決めた内容で、SNS用のカルーセル（Canvaで作る数ページの画像。MP4で提出）と投稿文を作る。実際には公開しない。
-わからない時はGeminiで自分で解決し、出てきた答えや式は必ず確かめる。</t>
+          <t>マーケティング手法をビジネスで活用するための基礎を養成する科目。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -668,10 +665,11 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. 目的に合う形式でGoogleフォームのアンケートを作れる。
-2. 回答をスプレッドシートで正しく集計できる（Geminiが作った式を検算する）。
-3. 集計結果から、ターゲット・内容・日時・投稿先を決められる。
-4. 決めた内容どおりのカルーセルと投稿文を作れる。</t>
+          <t>1. Googleフォームとスプレッドシートを使って、アンケートの集計結果から告知スライドが作成できる。
+2. GeminiとCanvaを使って、集計した数字を載せたカルーセル動画が作成できる。
+3. Googleマップと画像生成を使って、ターゲットと競合を踏まえたカルーセル動画が作成できる。
+4. GoogleトレンドとGA4を使って、投稿先と日時を決めたカルーセル動画と投稿文が作成できる。
+5. アンケートの集計結果を使って、「誰に・何を・いつ・どこで」を決めたカルーセル動画と投稿文が作成できる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1676,10 +1674,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>架空の学校の図書室や事務室から「利用ルールの張り紙を作り、利用記録を集計してほしい」と頼まれた設定で進める。
-先輩がAIで作った下書きをルールの原文だけを正として直し、張り紙（Googleドキュメント）・Googleスライド・集計表（スプレッドシート）・画像の4つを作る。
-作ったものは共有設定とGoogleフォームで提出する。回が進むとGmailでの納品やGoogleカレンダーの招待が加わる。
-わからない時はGeminiで自分で解決し、出てきた答えや式は必ず確かめる。</t>
+          <t>生成AIをビジネスで活用するための基礎を養成する科目。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -1758,10 +1753,11 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. ルールの原文だけを正として、AIの下書きの誤りを直した張り紙と誤り一覧を作成できる。
-2. Geminiに作らせた式を検算し、行を足しても正しく動く集計表をスプレッドシートで作成できる。
-3. 条件を守った画像を3枚そろえ、約束どおりの形のGoogleスライドを作成できる。
-4. 作ったものを共有設定・Gmail・Googleカレンダーの招待で届けられる。</t>
+          <t>1. Geminiとドキュメント・スプレッドシートを使って、張り紙・スライド・集計表・画像の一式が作成できる。
+2. Gemini Notebookを使って、下書きの誤りを直した張り紙と、画像3枚をそろえたスライドが作成できる。
+3. Gmailを使って、誤り一覧を添えた張り紙一式が納品できる。
+4. GmailとGoogleカレンダーを使って、説明会のスライド・納品メール・Google Meet付きの招待が作成できる。
+5. Geminiを使って、原文だけを正とした張り紙・スライド・集計表・画像の一式が作成できる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -2854,10 +2850,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>架空の学内講座の運営を、前任者から引き継いだ設定で進める。
-届いたメール・運営のルール・申込データを読み、Gmailで日程確定や補欠のお知らせを送り、Google Meetで運営会議を開いて議事録とToDoを作る。
-Googleドライブの共有フォルダを整理して共有設定を直し、スプレッドシートで申込を数えて確定・補欠・費用を出す。成果物は5回（成果物2は2人1組）で、画面録画などを添えてGoogleフォームで提出する。
-わからない時はGeminiで自分で解決し、答えは運営のルールと照らして確かめる。</t>
+          <t>ITツールをビジネスで活用するための基礎を養成する科目。</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -2936,10 +2929,11 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. メールから最新の決定を拾い、下書きの誤りだけを直して、GmailでBCCなど正しい宛先で送れる。
-2. Google Meetで会議を開き、Googleドキュメントで議事録を作成し、ToDoの期限をGoogleカレンダーに入れられる。
-3. Googleドライブの共有フォルダを整理し、共有設定（リンク公開、閲覧者・編集者）を安全に直せる。
-4. Geminiが作った式をスプレッドシートで検算し、申込を数えて確定・補欠と費用を出せる。</t>
+          <t>1. Gmailを使って、複数のメールから拾った最新の日時・会場で日程確定のメールが送信できる。
+2. Google MeetとGoogleカレンダーを使って、会議の議事録作成とToDoの期限登録ができる。
+3. Googleドライブとスプレッドシートを使って、共有フォルダの整理と人数の報告ができる。
+4. スプレッドシートとGmailを使って、確定・補欠の決定とお知らせメールの予約送信ができる。
+5. スプレッドシートとGoogleドライブを使って、人数・印刷費の算出と安全な共有設定での引き継ぎができる。</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
